--- a/停電作業計画書_第2回_補給倉庫棟.xlsx
+++ b/停電作業計画書_第2回_補給倉庫棟.xlsx
@@ -28,13 +28,13 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'1.概要 2.工程管理'!$A$1:$J$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3.現場組織表'!$A$1:$G$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'4.緊急連絡表'!$A$1:$D$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.安全対策'!$A$1:$D$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.安全対策'!$A$1:$D$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'6.作業方法'!$A$1:$F$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'7.タイムスケジュール'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'7.タイムスケジュール'!$A$1:$I$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'8.配置図'!$A$1:$F$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'9.品質管理'!$A$1:$G$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'10.チェックリスト'!$A$1:$F$82</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'11.測定記録'!$A$1:$G$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'9.品質管理'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'10.チェックリスト'!$A$1:$F$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'11.測定記録'!$A$1:$G$97</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'12.作業員名簿'!$A$1:$H$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'※要確認事項'!$A$1:$D$20</definedName>
   </definedNames>
@@ -116,6 +116,15 @@
     <font>
       <name val="ＭＳ ゴシック"/>
       <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="ＭＳ 明朝"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="ＭＳ ゴシック"/>
+      <b val="1"/>
       <sz val="11.5"/>
     </font>
     <font>
@@ -124,18 +133,9 @@
       <sz val="8.5"/>
     </font>
     <font>
-      <name val="ＭＳ 明朝"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="ＭＳ ゴシック"/>
       <b val="1"/>
       <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="ＭＳ ゴシック"/>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -313,31 +313,31 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -890,7 +890,7 @@
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="8" t="n"/>
     </row>
-    <row r="13" ht="33.56" customHeight="1">
+    <row r="13" ht="47.84" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>停 電 作 業 日</t>
@@ -900,7 +900,7 @@
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>令和8年12月5日（土）・12月6日（日）　9:00～16:00
-（高圧は12/5　9:00から12/6の試験・検査終了後の復電まで連続停電）</t>
+（12/6は試験・検査終了後に復電、17:00頃終了予定。高圧は12/5　9:00から復電まで連続停電）</t>
         </is>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -1120,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1639,37 +1639,37 @@
       </c>
     </row>
     <row r="23" ht="29.48" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>管　理　項　目</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>管　理　基　準</t>
         </is>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="D23" s="37" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>確認日</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="F23" s="37" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="G23" s="37" t="inlineStr">
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1696,57 +1696,41 @@
       <c r="F24" s="25" t="inlineStr"/>
       <c r="G24" s="25" t="inlineStr"/>
     </row>
-    <row r="25" ht="29.48" customHeight="1">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>管　理　項　目</t>
-        </is>
-      </c>
-      <c r="B25" s="37" t="inlineStr">
-        <is>
-          <t>管　理　基　準</t>
-        </is>
-      </c>
-      <c r="C25" s="37" t="inlineStr">
-        <is>
-          <t>確認方法</t>
-        </is>
-      </c>
-      <c r="D25" s="37" t="inlineStr">
-        <is>
-          <t>確認日</t>
-        </is>
-      </c>
-      <c r="E25" s="37" t="inlineStr">
-        <is>
-          <t>合否</t>
-        </is>
-      </c>
-      <c r="F25" s="37" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-      <c r="G25" s="37" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+    <row r="25" ht="29.84" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>撤去前の結線状態の記録</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>写真・マーキングで記録したか</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>目視・写真</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr"/>
+      <c r="E25" s="25" t="inlineStr"/>
+      <c r="F25" s="25" t="inlineStr"/>
+      <c r="G25" s="25" t="inlineStr"/>
     </row>
     <row r="26" ht="29.84" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>撤去前の結線状態の記録</t>
+          <t>揚重作業の安全確認</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>写真・マーキングで記録したか</t>
+          <t>有資格者・合図者の配置、吊具・ユニック車の点検</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>目視・写真</t>
+          <t>目視・記録</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr"/>
@@ -1757,17 +1741,17 @@
     <row r="27" ht="29.84" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>揚重作業の安全確認</t>
+          <t>変圧器の据付</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>有資格者・合図者の配置、吊具・ユニック車の点検</t>
+          <t>水平、防振ゴムの位置、架台・アンカーの締付</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>目視・記録</t>
+          <t>計測・トルク</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr"/>
@@ -1778,17 +1762,17 @@
     <row r="28" ht="29.84" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>変圧器の据付</t>
+          <t>変圧器のタップ位置</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>水平、防振ゴムの位置、架台・アンカーの締付</t>
+          <t>設計図書・監督官指示のとおりか</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>計測・トルク</t>
+          <t>目視・記録</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr"/>
@@ -1799,17 +1783,17 @@
     <row r="29" ht="29.84" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>変圧器のタップ位置</t>
+          <t>高圧機器の取付</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>設計図書・監督官指示のとおりか</t>
+          <t>水平、固定ボルトの締付、パネルカット部の処理</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>目視・記録</t>
+          <t>計測・トルク</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr"/>
@@ -1817,20 +1801,20 @@
       <c r="F29" s="25" t="inlineStr"/>
       <c r="G29" s="25" t="inlineStr"/>
     </row>
-    <row r="30" ht="29.84" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>高圧機器の取付</t>
+          <t>端子の締付トルク</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>水平、固定ボルトの締付、パネルカット部の処理</t>
+          <t>機器指定トルク値</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>計測・トルク</t>
+          <t>トルクレンチ</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr"/>
@@ -1841,17 +1825,17 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>端子の締付トルク</t>
+          <t>増締めチェック</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>機器指定トルク値</t>
+          <t>チェックマークの表示</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>トルクレンチ</t>
+          <t>目視</t>
         </is>
       </c>
       <c r="D31" s="25" t="inlineStr"/>
@@ -1859,20 +1843,20 @@
       <c r="F31" s="25" t="inlineStr"/>
       <c r="G31" s="25" t="inlineStr"/>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="29.84" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>増締めチェック</t>
+          <t>相順・結線の確認</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>チェックマークの表示</t>
+          <t>R・S・T/U・V・Wの相順が正しいか</t>
         </is>
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>目視</t>
+          <t>検相器・目視</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr"/>
@@ -1883,17 +1867,17 @@
     <row r="33" ht="29.84" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>相順・結線の確認</t>
+          <t>2次導体の接続時期</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>R・S・T/U・V・Wの相順が正しいか</t>
+          <t>母線側は仮設発電機の停止・切離し後に接続したか</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>検相器・目視</t>
+          <t>目視・記録</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr"/>
@@ -1904,17 +1888,17 @@
     <row r="34" ht="29.84" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>2次導体の接続時期</t>
+          <t>接地線の接続</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>母線側は仮設発電機の停止・切離し後に接続したか</t>
+          <t>EA・EB・EDが確実に接続されているか</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>目視・記録</t>
+          <t>目視・計測</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr"/>
@@ -1925,17 +1909,17 @@
     <row r="35" ht="29.84" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>接地線の接続</t>
+          <t>温度計配線</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>EA・EB・EDが確実に接続されているか</t>
+          <t>ダイヤル温度計（警報接点）の結線及び動作</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>目視・計測</t>
+          <t>目視・動作</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr"/>
@@ -1946,17 +1930,17 @@
     <row r="36" ht="29.84" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>温度計配線</t>
+          <t>シーケンス試験</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>ダイヤル温度計（警報接点）の結線及び動作</t>
+          <t>VCB投入・引外し、常用/予備インターロック</t>
         </is>
       </c>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>目視・動作</t>
+          <t>動作確認</t>
         </is>
       </c>
       <c r="D36" s="25" t="inlineStr"/>
@@ -1967,17 +1951,17 @@
     <row r="37" ht="29.84" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>シーケンス試験</t>
+          <t>絶縁抵抗</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>VCB投入・引外し、常用/予備インターロック</t>
+          <t>電気設備技術基準（省令第58条）及び設計図書による</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>動作確認</t>
+          <t>絶縁抵抗計</t>
         </is>
       </c>
       <c r="D37" s="25" t="inlineStr"/>
@@ -1988,17 +1972,17 @@
     <row r="38" ht="29.84" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>絶縁抵抗</t>
+          <t>接地抵抗</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>電気設備技術基準（省令第58条）及び設計図書による</t>
+          <t>A種10Ω以下　/　D種100Ω以下</t>
         </is>
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>絶縁抵抗計</t>
+          <t>接地抵抗計</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr"/>
@@ -2009,17 +1993,17 @@
     <row r="39" ht="29.84" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>接地抵抗</t>
+          <t>絶縁耐力試験</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>A種10Ω以下　/　D種100Ω以下</t>
+          <t>規定電圧を10分間印加し異常のないこと</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>接地抵抗計</t>
+          <t>試験装置</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr"/>
@@ -2030,17 +2014,17 @@
     <row r="40" ht="29.84" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>絶縁耐力試験</t>
+          <t>保護継電器試験</t>
         </is>
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>規定電圧を10分間印加し異常のないこと</t>
+          <t>整定値どおりに動作すること（OCR・UVR）</t>
         </is>
       </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>試験装置</t>
+          <t>継電器試験器</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr"/>
@@ -2051,17 +2035,17 @@
     <row r="41" ht="29.84" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>保護継電器試験</t>
+          <t>復電後の電圧・相回転</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>整定値どおりに動作すること（OCR・UVR）</t>
+          <t>規定電圧範囲内、相回転が正相であること</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>継電器試験器</t>
+          <t>電圧計・検相器</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr"/>
@@ -2072,17 +2056,17 @@
     <row r="42" ht="29.84" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>復電後の電圧・相回転</t>
+          <t>盤内の清掃・残置物</t>
         </is>
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>規定電圧範囲内、相回転が正相であること</t>
+          <t>工具・ウエス・切粉等の残置がないこと</t>
         </is>
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>電圧計・検相器</t>
+          <t>目視</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr"/>
@@ -2093,17 +2077,17 @@
     <row r="43" ht="29.84" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>盤内の清掃・残置物</t>
+          <t>仮設発電機の運転状態</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>工具・ウエス・切粉等の残置がないこと</t>
+          <t>電圧・周波数・燃料残量が適正か</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>目視</t>
+          <t>目視・計測</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr"/>
@@ -2111,107 +2095,111 @@
       <c r="F43" s="25" t="inlineStr"/>
       <c r="G43" s="25" t="inlineStr"/>
     </row>
-    <row r="44" ht="29.84" customHeight="1">
-      <c r="A44" s="26" t="inlineStr">
-        <is>
-          <t>仮設発電機の運転状態</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>電圧・周波数・燃料残量が適正か</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>目視・計測</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr"/>
-      <c r="E44" s="25" t="inlineStr"/>
-      <c r="F44" s="25" t="inlineStr"/>
-      <c r="G44" s="25" t="inlineStr"/>
-    </row>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+    <row r="44" ht="12" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>9.3　撮影対象表</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18.6" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
+    <row r="46" ht="18.6" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>工事種目又は分類</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>撮　影　対　象</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>撮影時期</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>摘　要</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="31.2" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>着工前</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>作業場所全景、既設キュービクル外観・盤内</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="8" t="n"/>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>撮影時期</t>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>着工前</t>
         </is>
       </c>
       <c r="F47" s="8" t="n"/>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>摘　要</t>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>代表各1枚</t>
         </is>
       </c>
     </row>
     <row r="48" ht="31.2" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>着工前</t>
+          <t>仮設工事</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>作業場所全景、既設キュービクル外観・盤内</t>
+          <t>発電機据付状況、仮設ケーブル敷設状況、仮設接地、単体試運転</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>着工前</t>
+          <t>施工中</t>
         </is>
       </c>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>代表各1枚</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="31.2" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>仮設工事</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>発電機据付状況、仮設ケーブル敷設状況、仮設接地、単体試運転</t>
+          <t>各1枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18.6" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>工事種目又は分類</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>撮　影　対　象</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="8" t="n"/>
-      <c r="E49" s="21" t="inlineStr">
-        <is>
-          <t>施工中</t>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>撮影時期</t>
         </is>
       </c>
       <c r="F49" s="8" t="n"/>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>各1枚</t>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>摘　要</t>
         </is>
       </c>
     </row>
@@ -2240,47 +2228,47 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="18.6" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>工事種目又は分類</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>撮　影　対　象</t>
+    <row r="51" ht="31.2" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>撤去工事</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>撤去前の状況、解体・分別・搬出の状況</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="8" t="n"/>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>撮影時期</t>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>撤去前・撤去中・撤去後</t>
         </is>
       </c>
       <c r="F51" s="8" t="n"/>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>摘　要</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="31.2" customHeight="1">
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>各1枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>撤去工事</t>
+          <t>揚重作業</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>撤去前の状況、解体・分別・搬出の状況</t>
+          <t>吊具の取付状況、玉掛け・揚重状況、搬出入状況</t>
         </is>
       </c>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>撤去前・撤去中・撤去後</t>
+          <t>施工中</t>
         </is>
       </c>
       <c r="F52" s="8" t="n"/>
@@ -2290,15 +2278,15 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="31.2" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>揚重作業</t>
+          <t>据付工事</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>吊具の取付状況、玉掛け・揚重状況、搬出入状況</t>
+          <t>新設機器の搬入・据付、防振ゴム、架台・アンカー、水平確認</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
@@ -2311,19 +2299,19 @@
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="21" t="inlineStr">
         <is>
-          <t>各1枚</t>
+          <t>代表各1枚</t>
         </is>
       </c>
     </row>
     <row r="54" ht="31.2" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>据付工事</t>
+          <t>結線工事</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>新設機器の搬入・据付、防振ゴム、架台・アンカー、水平確認</t>
+          <t>母線接続、端子締付、増締めチェック、相順確認、タップ位置</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
@@ -2340,15 +2328,15 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="31.2" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>結線工事</t>
+          <t>接地工事</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>母線接続、端子締付、増締めチェック、相順確認、タップ位置</t>
+          <t>接地線接続状況、接地抵抗測定</t>
         </is>
       </c>
       <c r="C55" s="10" t="n"/>
@@ -2361,26 +2349,26 @@
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="21" t="inlineStr">
         <is>
-          <t>代表各1枚</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
+          <t>各1枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="31.2" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>接地工事</t>
+          <t>試　験</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>接地線接続状況、接地抵抗測定</t>
+          <t>絶縁抵抗測定、絶縁耐力試験、継電器試験、電圧・相回転測定</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>施工中</t>
+          <t>試験毎に1回</t>
         </is>
       </c>
       <c r="F56" s="8" t="n"/>
@@ -2393,19 +2381,19 @@
     <row r="57" ht="31.2" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>試　験</t>
+          <t>復　電</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>絶縁抵抗測定、絶縁耐力試験、継電器試験、電圧・相回転測定</t>
+          <t>受電所送り出し遮断器投入状況、VCB投入、負荷復旧・機能確認</t>
         </is>
       </c>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="21" t="inlineStr">
         <is>
-          <t>試験毎に1回</t>
+          <t>施工中</t>
         </is>
       </c>
       <c r="F57" s="8" t="n"/>
@@ -2415,22 +2403,22 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="31.2" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>復　電</t>
+          <t>仮設撤去</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>受電所送り出し遮断器投入状況、VCB投入、負荷復旧・機能確認</t>
+          <t>撤去状況、原状復旧後の状況</t>
         </is>
       </c>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="21" t="inlineStr">
         <is>
-          <t>施工中</t>
+          <t>撤去中・撤去後</t>
         </is>
       </c>
       <c r="F58" s="8" t="n"/>
@@ -2443,19 +2431,19 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>仮設撤去</t>
+          <t>発生材</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>撤去状況、原状復旧後の状況</t>
+          <t>分別・集積状況、搬出状況</t>
         </is>
       </c>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="21" t="inlineStr">
         <is>
-          <t>撤去中・撤去後</t>
+          <t>搬出前・搬出時</t>
         </is>
       </c>
       <c r="F59" s="8" t="n"/>
@@ -2465,58 +2453,33 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="31.2" customHeight="1">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>発生材</t>
+          <t>完　成</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>分別・集積状況、搬出状況</t>
+          <t>完成全景、盤内完成状況</t>
         </is>
       </c>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>搬出前・搬出時</t>
+          <t>完成後</t>
         </is>
       </c>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="21" t="inlineStr">
         <is>
-          <t>各1枚</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="31.2" customHeight="1">
-      <c r="A61" s="21" t="inlineStr">
-        <is>
-          <t>完　成</t>
-        </is>
-      </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>完成全景、盤内完成状況</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="21" t="inlineStr">
-        <is>
-          <t>完成後</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="21" t="inlineStr">
-        <is>
           <t>代表各1枚</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18.6" customHeight="1">
-      <c r="A62" s="23" t="inlineStr">
+    <row r="61" ht="18.6" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>※　写真管理は蔵衛門Padによる。立入管理区域においては、申請を行ったデジタルカメラを使用する。</t>
         </is>
@@ -2531,10 +2494,8 @@
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B61:D61"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A62:G62"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="E52:F52"/>
@@ -2549,23 +2510,25 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E59:F59"/>
+    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E46:F46"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E61:F61"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A46:G46"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E14:G14"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="B56:D56"/>
@@ -2590,8 +2553,8 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="24" min="0" max="16383" man="1"/>
-    <brk id="50" min="0" max="16383" man="1"/>
+    <brk id="21" min="0" max="16383" man="1"/>
+    <brk id="48" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2602,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2629,7 +2592,7 @@
     </row>
     <row r="3" ht="10" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>10.1　作業開始前（毎日）</t>
         </is>
@@ -2877,7 +2840,7 @@
     </row>
     <row r="19" ht="10" customHeight="1"/>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>10.2　停電操作時</t>
         </is>
@@ -3125,7 +3088,7 @@
     </row>
     <row r="34" ht="10" customHeight="1"/>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>10.3　仮設送電時</t>
         </is>
@@ -3293,7 +3256,7 @@
     </row>
     <row r="45" ht="10" customHeight="1"/>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>10.4　作業中（撤去・据付）・夜間</t>
         </is>
@@ -3525,7 +3488,7 @@
     </row>
     <row r="60" ht="10" customHeight="1"/>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>10.5　復電前</t>
         </is>
@@ -3725,7 +3688,7 @@
     </row>
     <row r="73" ht="10" customHeight="1"/>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>10.6　復電後・終業時</t>
         </is>
@@ -3763,7 +3726,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="29.84" customHeight="1">
+    <row r="76" ht="42.76" customHeight="1">
       <c r="A76" s="25" t="inlineStr">
         <is>
           <t>1</t>
@@ -3771,7 +3734,7 @@
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>高圧復電後（LBS開放のまま）、電圧及び常用/予備の切替動作・相回転一致を確認し記録したか</t>
+          <t>発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続を、高圧停電・作業用接地中に完了したか</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr"/>
@@ -3779,7 +3742,7 @@
       <c r="E76" s="25" t="inlineStr"/>
       <c r="F76" s="25" t="inlineStr"/>
     </row>
-    <row r="77" ht="42.76" customHeight="1">
+    <row r="77" ht="29.84" customHeight="1">
       <c r="A77" s="25" t="inlineStr">
         <is>
           <t>2</t>
@@ -3787,7 +3750,7 @@
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>発電機を停止し仮設ケーブルを切り離してから、2次導体母線側を接続し、LBSを1台ずつ投入・主幹を投入したか</t>
+          <t>高圧復電後（LBS開放のまま）、電圧及び常用/予備の切替動作・相回転一致を確認し記録したか</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr"/>
@@ -3803,7 +3766,7 @@
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>負荷を順次投入し、補給倉庫棟の機能の正常を部隊立会のもと確認したか</t>
+          <t>LBSを1台ずつ投入し（変圧器の異音・励磁状態確認）、主幹を投入したか。復電後に盤内作業を行っていないか</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr"/>
@@ -3811,7 +3774,7 @@
       <c r="E78" s="25" t="inlineStr"/>
       <c r="F78" s="25" t="inlineStr"/>
     </row>
-    <row r="79" ht="21" customHeight="1">
+    <row r="79" ht="29.84" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
         <is>
           <t>4</t>
@@ -3819,7 +3782,7 @@
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>変圧器の温度計・警報接点の動作を確認したか</t>
+          <t>負荷を順次投入し、補給倉庫棟の機能の正常を部隊立会のもと確認したか</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr"/>
@@ -3835,7 +3798,7 @@
       </c>
       <c r="B80" s="26" t="inlineStr">
         <is>
-          <t>操作禁止札・施錠具を撤去したか</t>
+          <t>変圧器の温度計・警報接点の動作を確認したか</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr"/>
@@ -3851,7 +3814,7 @@
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>測定記録・写真を整理し、監督官の確認を受けたか</t>
+          <t>操作禁止札・施錠具を撤去したか</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr"/>
@@ -3867,13 +3830,29 @@
       </c>
       <c r="B82" s="26" t="inlineStr">
         <is>
-          <t>現場を清掃し、安全施設を適正な状態に戻したか</t>
+          <t>測定記録・写真を整理し、監督官の確認を受けたか</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr"/>
       <c r="D82" s="25" t="inlineStr"/>
       <c r="E82" s="25" t="inlineStr"/>
       <c r="F82" s="25" t="inlineStr"/>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>現場を清掃し、安全施設を適正な状態に戻したか</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr"/>
+      <c r="D83" s="25" t="inlineStr"/>
+      <c r="E83" s="25" t="inlineStr"/>
+      <c r="F83" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3910,7 +3889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3929,10 +3908,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32.2" customHeight="1">
+    <row r="2" ht="18.6" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>工事名:舞鶴外（6）照明改修等電気その他工事　　作業場所:海上自衛隊　舞鶴航空基地　補給倉庫棟　電気室（京都府舞鶴市）</t>
+          <t>工事名:舞鶴外（6）照明改修等電気その他工事　　作業場所:舞鶴航空基地　補給倉庫棟　電気室</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3938,7 @@
     </row>
     <row r="4" ht="10" customHeight="1"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>11.1　作業用接地（短絡接地器具）　取付・取外し記録</t>
         </is>
@@ -4080,7 +4059,7 @@
     </row>
     <row r="13" ht="10" customHeight="1"/>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>11.2　締付トルク・タップ位置記録</t>
         </is>
@@ -4306,7 +4285,7 @@
     </row>
     <row r="27" ht="10" customHeight="1"/>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>11.3　絶縁抵抗測定記録</t>
         </is>
@@ -4601,118 +4580,106 @@
       <c r="F41" s="25" t="inlineStr"/>
       <c r="G41" s="25" t="inlineStr"/>
     </row>
-    <row r="42" ht="29.84" customHeight="1">
+    <row r="42" ht="42.76" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>仮設ケーブル（CET150sq×6条）</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>DC500V</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>0.2MΩ以上</t>
-        </is>
-      </c>
+          <t>（低圧母線②③④は12/6　発電機切離し後・2次導体接続前に測定）</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr"/>
+      <c r="C42" s="25" t="inlineStr"/>
       <c r="D42" s="25" t="inlineStr"/>
       <c r="E42" s="25" t="inlineStr"/>
       <c r="F42" s="25" t="inlineStr"/>
       <c r="G42" s="25" t="inlineStr"/>
     </row>
-    <row r="43" ht="30.84" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+    <row r="43" ht="29.84" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>仮設ケーブル　CET150sq×6条</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>DC500V</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>0.2MΩ以上</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr"/>
+      <c r="E43" s="25" t="inlineStr"/>
+      <c r="F43" s="25" t="inlineStr"/>
+      <c r="G43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30.84" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>※　基準値は電気設備に関する技術基準を定める省令第58条による（対地電圧150V以下:0.1MΩ、300V以下:0.2MΩ、300V超:0.4MΩ）。高圧は設計図書・保安協会の基準による。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="10" customHeight="1"/>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>11.4　接地抵抗測定記録</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>測　定　箇　所</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>接地種別</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>基 準 値</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>測 定 値</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>測定方法</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="G46" s="24" t="inlineStr">
+      <c r="G47" s="24" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>EA（高圧機器外箱）</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>A種</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>10Ω以下</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr"/>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>電位差法</t>
-        </is>
-      </c>
-      <c r="F47" s="21" t="inlineStr"/>
-      <c r="G47" s="21" t="inlineStr"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>EB（変圧器二次側）</t>
+          <t>EA（高圧機器外箱）</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>B種</t>
+          <t>A種</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>計算値による</t>
+          <t>10Ω以下</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr"/>
@@ -4727,17 +4694,17 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>ED（低圧機器外箱）</t>
+          <t>EB（変圧器二次側）</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>D種</t>
+          <t>B種</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>100Ω以下</t>
+          <t>計算値による</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr"/>
@@ -4752,7 +4719,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>仮設発電機1号機　接地</t>
+          <t>ED（低圧機器外箱）</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
@@ -4777,7 +4744,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>仮設発電機2号機　接地</t>
+          <t>仮設発電機1号機　接地</t>
         </is>
       </c>
       <c r="B51" s="21" t="inlineStr">
@@ -4799,72 +4766,80 @@
       <c r="F51" s="21" t="inlineStr"/>
       <c r="G51" s="21" t="inlineStr"/>
     </row>
-    <row r="52" ht="10" customHeight="1"/>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>仮設発電機2号機　接地</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>D種</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>100Ω以下</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr"/>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>電位差法</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr"/>
+      <c r="G52" s="21" t="inlineStr"/>
+    </row>
+    <row r="53" ht="10" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>11.5　絶縁耐力試験記録</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>試　験　対　象</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B55" s="24" t="inlineStr">
         <is>
           <t>試験電圧</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>印加時間</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>開始時刻</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>終了時刻</t>
         </is>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="F55" s="24" t="inlineStr">
         <is>
           <t>結　果</t>
         </is>
       </c>
-      <c r="G54" s="24" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="31.2" customHeight="1">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>高圧回路（母線・機器一括）</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="inlineStr"/>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>10分間</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr"/>
-      <c r="E55" s="21" t="inlineStr"/>
-      <c r="F55" s="21" t="inlineStr"/>
-      <c r="G55" s="21" t="inlineStr"/>
     </row>
     <row r="56" ht="31.2" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>高圧引込ケーブル（常用線・予備線）</t>
+          <t>高圧回路（母線・機器一括）</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr"/>
@@ -4876,46 +4851,26 @@
       <c r="D56" s="21" t="inlineStr"/>
       <c r="E56" s="21" t="inlineStr"/>
       <c r="F56" s="21" t="inlineStr"/>
-      <c r="G56" s="21" t="inlineStr">
+      <c r="G56" s="21" t="inlineStr"/>
+    </row>
+    <row r="57" ht="31.2" customHeight="1">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>高圧引込ケーブル（常用線・予備線）</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="inlineStr"/>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>10分間</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr"/>
+      <c r="E57" s="21" t="inlineStr"/>
+      <c r="F57" s="21" t="inlineStr"/>
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>接地一時取外し</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
-        <is>
-          <t>試　験　対　象</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>試験電圧</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>印加時間</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>開始時刻</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>終了時刻</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>結　果</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4900,7 @@
     </row>
     <row r="60" ht="10" customHeight="1"/>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>11.6　保護継電器・シーケンス試験記録</t>
         </is>
@@ -5047,7 +5002,7 @@
     <row r="67" ht="31.2" customHeight="1">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>変圧器　温度計警報接点（T-1～T-3）</t>
+          <t>変圧器温度計警報接点　T-1～3</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr"/>
@@ -5059,7 +5014,7 @@
     </row>
     <row r="68" ht="10" customHeight="1"/>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>11.7　復電時　電圧・相回転測定記録</t>
         </is>
@@ -5237,48 +5192,48 @@
     </row>
     <row r="78" ht="10" customHeight="1"/>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="32" t="inlineStr">
         <is>
           <t>11.8　仮設発電機　運転記録</t>
         </is>
       </c>
     </row>
     <row r="80" ht="41.72" customHeight="1">
-      <c r="A80" s="37" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>日　時</t>
         </is>
       </c>
-      <c r="B80" s="37" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>1号機
 電圧・電流</t>
         </is>
       </c>
-      <c r="C80" s="37" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>1号機
 周波数・燃料</t>
         </is>
       </c>
-      <c r="D80" s="37" t="inlineStr">
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>2号機
 電圧・電流</t>
         </is>
       </c>
-      <c r="E80" s="37" t="inlineStr">
+      <c r="E80" s="29" t="inlineStr">
         <is>
           <t>2号機
 周波数・燃料</t>
         </is>
       </c>
-      <c r="F80" s="37" t="inlineStr">
+      <c r="F80" s="29" t="inlineStr">
         <is>
           <t>油漏れ・異音</t>
         </is>
       </c>
-      <c r="G80" s="37" t="inlineStr">
+      <c r="G80" s="29" t="inlineStr">
         <is>
           <t>記録者</t>
         </is>
@@ -5349,51 +5304,23 @@
       <c r="F85" s="25" t="inlineStr"/>
       <c r="G85" s="25" t="inlineStr"/>
     </row>
-    <row r="86" ht="41.72" customHeight="1">
-      <c r="A86" s="37" t="inlineStr">
-        <is>
-          <t>日　時</t>
-        </is>
-      </c>
-      <c r="B86" s="37" t="inlineStr">
-        <is>
-          <t>1号機
-電圧・電流</t>
-        </is>
-      </c>
-      <c r="C86" s="37" t="inlineStr">
-        <is>
-          <t>1号機
-周波数・燃料</t>
-        </is>
-      </c>
-      <c r="D86" s="37" t="inlineStr">
-        <is>
-          <t>2号機
-電圧・電流</t>
-        </is>
-      </c>
-      <c r="E86" s="37" t="inlineStr">
-        <is>
-          <t>2号機
-周波数・燃料</t>
-        </is>
-      </c>
-      <c r="F86" s="37" t="inlineStr">
-        <is>
-          <t>油漏れ・異音</t>
-        </is>
-      </c>
-      <c r="G86" s="37" t="inlineStr">
-        <is>
-          <t>記録者</t>
-        </is>
-      </c>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>12/5　20:00</t>
+        </is>
+      </c>
+      <c r="B86" s="25" t="inlineStr"/>
+      <c r="C86" s="25" t="inlineStr"/>
+      <c r="D86" s="25" t="inlineStr"/>
+      <c r="E86" s="25" t="inlineStr"/>
+      <c r="F86" s="25" t="inlineStr"/>
+      <c r="G86" s="25" t="inlineStr"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>12/5　20:00</t>
+          <t>12/5　22:00</t>
         </is>
       </c>
       <c r="B87" s="25" t="inlineStr"/>
@@ -5406,7 +5333,7 @@
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>12/5　22:00</t>
+          <t>12/6　0:00</t>
         </is>
       </c>
       <c r="B88" s="25" t="inlineStr"/>
@@ -5419,7 +5346,7 @@
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>12/6　0:00</t>
+          <t>12/6　2:00</t>
         </is>
       </c>
       <c r="B89" s="25" t="inlineStr"/>
@@ -5432,7 +5359,7 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>12/6　2:00</t>
+          <t>12/6　4:00</t>
         </is>
       </c>
       <c r="B90" s="25" t="inlineStr"/>
@@ -5445,7 +5372,7 @@
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>12/6　4:00</t>
+          <t>12/6　6:00</t>
         </is>
       </c>
       <c r="B91" s="25" t="inlineStr"/>
@@ -5458,7 +5385,7 @@
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="26" t="inlineStr">
         <is>
-          <t>12/6　6:00</t>
+          <t>12/6　8:00</t>
         </is>
       </c>
       <c r="B92" s="25" t="inlineStr"/>
@@ -5471,7 +5398,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>12/6　8:00</t>
+          <t>12/6　10:00</t>
         </is>
       </c>
       <c r="B93" s="25" t="inlineStr"/>
@@ -5484,7 +5411,7 @@
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>12/6　10:00</t>
+          <t>12/6　12:00</t>
         </is>
       </c>
       <c r="B94" s="25" t="inlineStr"/>
@@ -5497,7 +5424,7 @@
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>12/6　12:00</t>
+          <t>12/6　14:00</t>
         </is>
       </c>
       <c r="B95" s="25" t="inlineStr"/>
@@ -5507,10 +5434,10 @@
       <c r="F95" s="25" t="inlineStr"/>
       <c r="G95" s="25" t="inlineStr"/>
     </row>
-    <row r="96" ht="20" customHeight="1">
+    <row r="96" ht="29.84" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>12/6　14:00</t>
+          <t>12/6　15:45（運転停止）</t>
         </is>
       </c>
       <c r="B96" s="25" t="inlineStr"/>
@@ -5520,34 +5447,8 @@
       <c r="F96" s="25" t="inlineStr"/>
       <c r="G96" s="25" t="inlineStr"/>
     </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>12/6　16:00</t>
-        </is>
-      </c>
-      <c r="B97" s="25" t="inlineStr"/>
-      <c r="C97" s="25" t="inlineStr"/>
-      <c r="D97" s="25" t="inlineStr"/>
-      <c r="E97" s="25" t="inlineStr"/>
-      <c r="F97" s="25" t="inlineStr"/>
-      <c r="G97" s="25" t="inlineStr"/>
-    </row>
-    <row r="98" ht="29.84" customHeight="1">
-      <c r="A98" s="26" t="inlineStr">
-        <is>
-          <t>12/6　　:　（運転停止）</t>
-        </is>
-      </c>
-      <c r="B98" s="25" t="inlineStr"/>
-      <c r="C98" s="25" t="inlineStr"/>
-      <c r="D98" s="25" t="inlineStr"/>
-      <c r="E98" s="25" t="inlineStr"/>
-      <c r="F98" s="25" t="inlineStr"/>
-      <c r="G98" s="25" t="inlineStr"/>
-    </row>
-    <row r="99" ht="30.84" customHeight="1">
-      <c r="A99" s="28" t="inlineStr">
+    <row r="97" ht="30.84" customHeight="1">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>※　運転中は2時間毎に確認し記録する（電圧V/電流A、周波数Hz/燃料残量Lを記入）。12/5　16:00～12/6　8:30は夜間監視員が記録する。異常時は直ちに作業指揮者へ報告する。</t>
         </is>
@@ -5556,22 +5457,22 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A77:G77"/>
     <mergeCell ref="A69:G69"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A77:G77"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A54:G54"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
@@ -5586,8 +5487,8 @@
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="27" min="0" max="16383" man="1"/>
-    <brk id="56" min="0" max="16383" man="1"/>
-    <brk id="85" min="0" max="16383" man="1"/>
+    <brk id="53" min="0" max="16383" man="1"/>
+    <brk id="78" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -6509,7 +6410,7 @@
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>1000V/500V</t>
+          <t>1000V/500V/250V</t>
         </is>
       </c>
       <c r="G36" s="26" t="inlineStr">
@@ -6851,7 +6752,7 @@
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>CVCF室・電算機室等の停止できない負荷は現在調査中。結果により仮設切替時（12/5　9:00～10:30頃）・商用復旧時（12/6　16:15～16:45頃）の停電への対応（事前停止・UPS保持等）を定め、部隊の承諾を得る。</t>
+          <t>CVCF室・電算機室等の停止できない負荷は現在調査中。結果により仮設切替時（12/5　9:00～10:30頃）・商用復旧時（12/6　15:45～16:45頃）の停電への対応（事前停止・UPS保持等）を定め、部隊の承諾を得る。</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
@@ -6860,7 +6761,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42.76" customHeight="1">
+    <row r="6" ht="55.68" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
           <t>2</t>
@@ -6873,12 +6774,12 @@
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>1号機・2号機から各1条を④へ接続する計画。2台の発電機出力が同一母線で並列（非同期）とならないよう、接続点・分岐回路の振分けを確認する。</t>
+          <t>2台が並列とならないよう、1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続する計画とした。2号機で受け持つ分岐回路（負荷）と、その回路の負荷容量を確認する。</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>2.3・5.4・7・8</t>
+          <t>2.3・5.4・6.3・7・8</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6862,7 @@
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
-          <t>夜間監視員の氏名・人数・交代体制（日中作業者とは別）、及び発電機の燃料タンク容量と給油方法・給油時期を確定する。軽油の現場貯蔵が指定数量（1,000L）以上となる場合は消防署へ仮貯蔵・仮取扱いの承認申請を行う。</t>
+          <t>夜間監視員の氏名・人数・交代体制（日中作業者とは別）、及び発電機の燃料タンク容量と給油方法・給油時期を確定する。軽油は発電機タンク内を含め200L以上で少量危険物の届出、1,000L以上で消防署の仮貯蔵・仮取扱い承認が必要。</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
@@ -7036,7 +6937,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="19" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>10</t>
@@ -7124,7 +7025,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="19" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t>14</t>
@@ -8452,7 +8353,7 @@
         <is>
           <t>9:00～
 16:00
-（KY8:30～）</t>
+KY8:30～</t>
         </is>
       </c>
       <c r="I54" s="22" t="inlineStr">
@@ -8498,7 +8399,7 @@
       </c>
       <c r="J55" s="8" t="n"/>
     </row>
-    <row r="56" ht="140" customHeight="1">
+    <row r="56" ht="112.8" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
           <t>12月6日
@@ -8514,7 +8415,7 @@
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>新設機器取付・結線、高圧母線張替え、変圧器2次導体取替え（母線側は商用切替時に接続）、自主試験、関西電気保安協会による試験・検査（15:00頃～）、作業用接地取外し、受電所送り出し遮断器投入・DS・VCB投入（高圧復電）、発電機停止後に2次導体を接続しLBS投入・商用へ切替（当日復電）</t>
+          <t>新設機器取付・結線、高圧母線張替え、変圧器2次導体取替え、自主試験、関西電気保安協会による試験・検査（15:00頃～）、発電機停止・仮設切離し後に2次導体母線側を接続、作業用接地取外し、受電所送り出し遮断器・DS・VCB投入（高圧復電）、LBS投入・商用へ切替（当日復電）</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -8524,9 +8425,9 @@
         <is>
           <t>9:00～
 試験・検査
-終了後に復電
-（17:00頃
-終了予定）</t>
+後に復電
+17:00頃
+終了予定</t>
         </is>
       </c>
       <c r="I56" s="22" t="inlineStr">
@@ -8603,7 +8504,7 @@
     <row r="63" ht="45.8" customHeight="1">
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>④　停電の承諾　:　停電範囲・停電時間及び仮設発電機への切替時（12/5　9:00～10:30頃）・商用への復旧時（12/6　16:15～16:45頃）に生じる停電について、事前に部隊及び監督官の承諾を得る。なお、本停電により補給倉庫棟以外の建物が停電することはない。</t>
+          <t>④　停電の承諾　:　停電範囲・停電時間及び仮設発電機への切替時（12/5　9:00～10:30頃）・商用への復旧時（12/6　15:45～16:45頃）に生じる停電について、事前に部隊及び監督官の承諾を得る。なお、本停電により補給倉庫棟以外の建物が停電することはない。</t>
         </is>
       </c>
     </row>
@@ -8629,17 +8530,17 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="73" customHeight="1">
+    <row r="68" ht="86.59999999999999" customHeight="1">
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>①　仮設発電機400kVA×2台（三相出力・単相出力付）を補給倉庫棟外部に設置し、CET150sq（FEP100）×6条にて各盤の低圧側へ接続する（1号機→②2条・④1条/2号機→③2条・④1条）。接続点は②③が低圧母線（FBU負荷側）、④が52-L二次側（分岐母線）とし、変圧器2次導体（FBU）の取外しにより変圧器への逆送を防止する。低圧電灯盤④（1φ3W　210-105V）へは発電機の単相出力より送電する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45.8" customHeight="1">
+          <t>①　仮設発電機400kVA×2台（三相出力・単相出力付）を補給倉庫棟外部に設置し、CET150sq（FEP100）×6条にて各盤の低圧側へ接続する（1号機→②2条・④1条/2号機→③2条・④1条）。接続点は②③が低圧母線（FBU負荷側）、④は1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCBは開放・施錠）として2台が並列とならないようにし、変圧器2次導体（FBU）の取外しにより変圧器への逆送を防止する。低圧電灯盤④（1φ3W　210-105V）へは発電機の単相出力より送電する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="73" customHeight="1">
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>②　運転時間は12/5　10:30頃～12/6　16:15頃（夜間連続運転）とし、燃料は軽油6,758.4L（24時間×2日×2台×70.4L/h）を見込む。軽油の指定数量（1,000L）以上を現場に貯蔵しないよう分割補給とし、指定数量以上となる場合は所轄消防署へ仮貯蔵・仮取扱いの承認申請を行う。</t>
+          <t>②　運転時間は12/5　10:30頃～12/6　15:45頃（夜間連続運転）とし、燃料は軽油6,758.4L（24時間×2日×2台×70.4L/h）を見込む。軽油の指定数量（1,000L）以上を現場に貯蔵しないよう分割補給とし（発電機タンク内の燃料を含めて算定）、指定数量の1/5（200L）以上は火災予防条例による少量危険物の届出を行う。指定数量以上となる場合は所轄消防署へ仮貯蔵・仮取扱いの承認申請を行う。</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9009,7 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>停電・復電操作（受電所送り出し遮断器・VCB・DS）、作業用接地の確認</t>
+          <t>停電・復電操作（受電所送り出し遮断器・VCB・DS・LBS）、作業用接地の確認</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9042,7 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>キュービクル改修（盤内高圧機器の撤去・据付・結線）</t>
+          <t>キュービクル改修（高圧機器の撤去・据付・結線）</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9427,7 @@
       </c>
       <c r="G25" s="26" t="inlineStr"/>
     </row>
-    <row r="26" ht="55.68" customHeight="1">
+    <row r="26" ht="42.76" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
           <t>夜間監視員</t>
@@ -9541,7 +9442,7 @@
       <c r="C26" s="25" t="inlineStr">
         <is>
           <t>1名以上
-（交代制）</t>
+交代制</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
@@ -9916,7 +9817,8 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>㈱別川製作所（キュービクル改修）</t>
+          <t>㈱別川製作所
+（キュービクル改修）</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10201,7 +10103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10224,36 +10126,36 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32.2" customHeight="1">
-      <c r="B3" s="23" t="inlineStr">
+    <row r="3" ht="30.84" customHeight="1">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>①　停電工事について、部隊・監督官及び作業関係者全員による作業内容・作業方法・事前準備内容の綿密な打合せを行う。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32.2" customHeight="1">
-      <c r="B4" s="23" t="inlineStr">
+    <row r="4" ht="30.84" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>②　停電作業当日は全員集合し、再度作業内容・作業方法及び注意事項を伝達徹底するとともに、全員によるKYミーティングを行う。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32.2" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+    <row r="5" ht="30.84" customHeight="1">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>③　作業計画書以外の作業、及び順序の異なる作業は行わない。変更が生じた場合は作業を中断し、作業指揮者の指示を受ける。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18.6" customHeight="1">
-      <c r="B6" s="23" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>④　新規入場者には入場時教育を実施し、必要な資格を有することを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32.2" customHeight="1">
-      <c r="B7" s="23" t="inlineStr">
+    <row r="7" ht="30.84" customHeight="1">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>⑤　元請・別川製作所・ARワーク・関西テクノの四者で作業手順と相互の立入禁止範囲を確認し、輻輳作業とならないよう調整する。</t>
         </is>
@@ -10267,50 +10169,50 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18.6" customHeight="1">
-      <c r="B10" s="23" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>①　停電・復電操作は電気主任技術者が行い、主任工事監督官の立会のもとで実施する。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="59.4" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+    <row r="11" ht="56.68" customHeight="1">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>②　停電操作は、補給倉庫棟のVCB（常用・予備）及びLBS（89-1～3）を開放したのち、受電所の送り出し遮断器を常用線・予備線とも開放し、施錠及び操作禁止札を取り付ける。続いて補給倉庫棟のDSを開放し、操作禁止札を取り付ける。受電所での操作時は受電所連絡員が同行し、電気室側と無線で開閉状態を相互確認する。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18.6" customHeight="1">
-      <c r="B12" s="23" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>③　開放位置及び停電範囲（2回線とも停電していること）を全員で確認する。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.2" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+    <row r="13" ht="30.84" customHeight="1">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>④　高圧検電器により常用線・予備線それぞれの引込側で無電圧を確認し、残留電荷を放電したうえで、短絡接地器具（作業用接地）を確実に取り付ける。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45.8" customHeight="1">
-      <c r="B14" s="23" t="inlineStr">
+    <row r="14" ht="43.76" customHeight="1">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>⑤　仮設発電機からの逆送を防止するため、各盤の変圧器2次導体（FBU）を取り外し、変圧器と低圧母線が切り離されたことを確認してから仮設ケーブルを接続する。新設2次導体は変圧器側のみ結線し、母線側は発電機停止・仮設ケーブル切離し後まで接続しない（母線側端部は絶縁養生）。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32.2" customHeight="1">
-      <c r="B15" s="23" t="inlineStr">
+    <row r="15" ht="30.84" customHeight="1">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>⑥　試験のため作業用接地を一時取り外す場合は、電気主任技術者の指示により行い、取外し・再取付の時刻と箇所を測定記録に記入する。試験中は試験区画を立入禁止とし、監視員を配置する。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32.2" customHeight="1">
-      <c r="B16" s="23" t="inlineStr">
+    <row r="16" ht="30.84" customHeight="1">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>⑦　作業用接地の取付位置・取外しは作業指揮者及び電気主任技術者が確認し、チェックリスト及び測定記録に記録する。</t>
         </is>
@@ -10324,50 +10226,50 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="32.2" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+    <row r="19" ht="30.84" customHeight="1">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>①　作業者全員を集合させ、各作業の終了、作業用接地の取外し、工具・材料の残置がないことを確認してから送電する。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32.2" customHeight="1">
-      <c r="B20" s="23" t="inlineStr">
+    <row r="20" ht="30.84" customHeight="1">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>②　復電前に絶縁抵抗測定を行い、規定値以上であることを確認する。関西電気保安協会による試験・検査の終了を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18.6" customHeight="1">
-      <c r="B21" s="23" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>③　復電は必ず各作業班からの完了報告を受け、問題がないことを確認したのち行う。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="45.8" customHeight="1">
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>④　復電は、補給倉庫棟のLBS・VCBが開放されていることを確認したうえで、受電所の送り出し遮断器（常用線・予備線）を投入し、常用線DS・VCBを投入して受電する。予備線はDS投入・VCB開放の待機状態とし、常用/予備の切替動作及び両回線の相回転一致を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="59.4" customHeight="1">
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>⑤　仮設発電機から商用への切替は、発電機の負荷側開閉器を開放し発電機を停止、仮設ケーブルを切り離したのち、新設2次導体（FBU）の母線側を接続（締付トルク記録）し、LBSを1台ずつ投入（変圧器の異音・励磁状態を確認）、主幹を投入する手順とし、発電機と商用が同時に接続されないことを確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18.6" customHeight="1">
-      <c r="B24" s="23" t="inlineStr">
+    <row r="22" ht="56.68" customHeight="1">
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>④　仮設発電機から商用への切替準備は、高圧が停電し作業用接地を取り付けている間に行う。発電機の負荷側開閉器を開放し発電機を停止、仮設ケーブルを切り離し、低圧母線の絶縁抵抗を測定したのち、新設2次導体（FBU）の母線側を接続（締付トルク記録）する。高圧充電後に盤内で2次導体の接続作業は行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="69.59999999999999" customHeight="1">
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>⑤　復電は、作業用接地の取外し及び補給倉庫棟のLBS・VCBの開放を確認したうえで、受電所の送り出し遮断器（常用線・予備線）を投入し、常用線DS・VCBを投入して受電する。予備線はDS投入・VCB開放の待機状態とし、常用/予備の切替動作及び両回線の相回転一致を確認したのち、LBSを1台ずつ投入（変圧器の異音・励磁状態を確認）し、主幹を投入する。復電後はLBS電源側等の高圧充電部に近接しないよう盤扉を閉じ、区画・表示を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>⑥　復電後は負荷を順次投入し、補給倉庫棟の機能の正常を部隊立会のもと確認する。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32.2" customHeight="1">
-      <c r="B25" s="23" t="inlineStr">
+    <row r="25" ht="30.84" customHeight="1">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>⑦　作業終了後は片付けを確実に行い、盤内の清掃、工具・ウエス等の残置確認（指差呼称）及び既設物の損傷の有無を確認する。</t>
         </is>
@@ -10382,303 +10284,320 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>想定される災害・リスク</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>対　　　　策</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42.76" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+    <row r="29" ht="40.72" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>高圧充電部への接近による感電</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>受電所送り出し遮断器開放・検電・放電・短絡接地の4点を必ず実施し、チェックリストで相互確認する。高圧絶縁用保護具及び絶縁用防具を着用する。</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>中村/足立</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="42.76" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+    <row r="30" ht="40.72" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>2回線受電による誤送電
 （予備線からの充電）</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>常用線・予備線の両方を開放・施錠し、両回線とも検電・短絡接地を行う。受電所側の操作禁止札の管理者を電気主任技術者とする。</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>足立</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="68.59999999999999" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+    <row r="31" ht="65.2" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>仮設発電機からの逆送
 （変圧器→高圧側への昇圧）</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>変圧器2次導体（FBU）の取外しを確認してから仮設ケーブルを接続する。新設2次導体の母線側は、発電機停止・仮設ケーブル切離しまで接続しない。仮設側と商用側の同時接続ができない措置（表示・施錠）をとる。No.2低圧動力盤③は主幹がないため特に注意する。</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="42.76" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+    <row r="32" ht="52.96" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>発電機の非同期並列</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>低圧電灯盤④へは1号機・2号機から各1条を接続するため、2台の発電機出力が同一母線で並列とならないよう、接続点・回路の振分けを事前に確認し表示する。</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>低圧電灯盤④へは1号機を52-L二次側（分岐母線）、2号機を特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続し、2台が同一母線で並列とならないことを確認・表示する。</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="55.68" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+    <row r="33" ht="40.72" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>復電後の高圧充電部への接近</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>2次導体の接続は高圧停電・作業用接地中に完了させ、復電後は盤内作業を行わない。やむを得ず盤内確認を行う場合は絶縁用防具を装着し、電気主任技術者の立会のもとで行う。</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52.96" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>重量物（変圧器等）の吊り荷
 落下・挟まれ・転倒</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>最大1,140kg（T-1）の変圧器は指定のつり耳を使用して吊り、吊り角度60度以内とする。吊り荷の下へ立ち入らせず、作業半径を区画する。玉掛け・クレーン運転は有資格者が行い、合図者を専任する。</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="42.76" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+    <row r="35" ht="28.48" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>2tユニック車の能力超過・転倒</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>吊り荷質量と作業半径から定格荷重を事前に確認し、アウトリガーを最大張出しで設置する。地盤・敷板を確認する。</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42.76" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
+    <row r="36" ht="40.72" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>チェーンブロック・台車での
 屋内搬出入</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>吊元の強度を事前に確認する。台車は重量物用を使用し、扉・通路の寸法と床の耐荷重を確認する。段差部は養生板を敷設し、転倒防止の介添えを付ける。</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42.76" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
+    <row r="37" ht="40.72" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>モールド変圧器の損傷</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>コイル部（モールド部）に衝撃・荷重を加えない。ワイヤーを直接コイルに掛けず、指定のつり耳のみを使用する。据付後は防振ゴムを正規位置に設置する。</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42.76" customHeight="1">
-      <c r="A37" s="26" t="inlineStr">
+    <row r="38" ht="40.72" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>発電機の夜間運転・給油時の火災、油流出</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>夜間監視員を配置し2時間毎に巡視する。給油は発電機停止又は規定の手順で行い、火気厳禁とする。オイルパン・吸着マット・消火器を設置する。</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="29.84" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
+    <row r="39" ht="28.48" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>盤上部・脚立からの墜落</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>脚立・可搬式作業台は使用前点検を行い、2m以上は墜落制止用器具を使用する。単独作業を禁止する。</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="29.84" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
+    <row r="40" ht="28.48" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>冬季の積雪・路面凍結</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>当日の気象情報を確認し、搬入路・揚重位置の除雪・凍結防止を行う。</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="29.84" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+    <row r="41" ht="28.48" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>低温による体調不良</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>防寒装備を着用し、暖を取れる休憩場所を確保する。作業間に小休止を入れる。</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>安全担当</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="29.84" customHeight="1">
-      <c r="A41" s="26" t="inlineStr">
+    <row r="42" ht="28.48" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>第三者・部隊車両の進入</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>カラーコーン・立入禁止表示により作業区画を明示し、監視員を配置する。</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>安全監視員</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42.76" customHeight="1">
-      <c r="A42" s="26" t="inlineStr">
+    <row r="43" ht="40.72" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>悪天候（強風・大雪・雷）</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>10分間平均風速10m/s以上、降雪25cm以上、雷光・雷鳴の間隔が短い場合は作業を中止する。特に揚重作業は風速10m/s以上で中止する。</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D43" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="12" customHeight="1"/>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="44" ht="12" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>5.5　保護具・安全器具</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="62.12" customHeight="1">
-      <c r="B45" s="16" t="inlineStr">
+    <row r="46" ht="62.12" customHeight="1">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>高圧絶縁用保護具（ヘルメット・絶縁手袋・絶縁長靴）、絶縁用防具、高圧検電器、放電棒、短絡接地器具（常用線・予備線用）、操作禁止札・施錠具、絶縁シート、墜落制止用器具、保護めがね、防寒具、カラーコーン・バリケード、消火器、投光器（冬季は日没が早いため必ず携行）、玉掛け用具（ナイロンスリング・シャックル）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A44:D44"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="B19:D19"/>
@@ -10689,8 +10608,8 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="A42:B42"/>
@@ -10704,6 +10623,8 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="B21:D21"/>
@@ -10881,7 +10802,7 @@
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>①作業前ミーティング・KY・夜間運転記録確認　→　②新設機器取付・結線（高圧受電盤）〔別川〕　→　③新設LBS取付・高圧母線（KIP）張替え〔別川〕　→　④変圧器固定・一次結線・新設2次導体の変圧器側結線（母線側は未接続・絶縁養生）・タップ設定・温度計配線〔別川・アート〕　→　⑤CT（L）・THR・MDA取替え〔別川〕　→　⑥接地線接続・盤内清掃　→　⑦自主試験（絶縁抵抗・シーケンス・インターロック）　→　⑧関西電気保安協会による試験・検査（15:00頃～、作業用接地は指示により一時取外し）　→　⑨作業用接地取外し・最終確認　→　⑩受電所送り出し遮断器投入・DS・VCB投入【高圧復電】・常用/予備切替確認　→　⑪発電機停止・仮設ケーブル切離し　→　⑫2次導体母線側接続・LBS順次投入・主幹投入【商用復旧】　→　⑬負荷・機能確認（部隊立会）・完了報告</t>
+          <t>①作業前ミーティング・KY・夜間運転記録確認　→　②新設機器取付・結線（高圧受電盤）〔別川〕　→　③新設LBS取付・高圧母線（KIP）張替え〔別川〕　→　④変圧器固定・一次結線・新設2次導体の変圧器側結線（母線側は未接続・絶縁養生）・タップ設定・温度計配線〔別川・アート〕　→　⑤CT（L）・THR・MDA取替え〔別川〕　→　⑥接地線接続・盤内清掃　→　⑦自主試験（絶縁抵抗・シーケンス・インターロック）　→　⑧関西電気保安協会による試験・検査（15:00頃～、作業用接地は指示により一時取外し）　→　⑨発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続（高圧停電・接地中）　→　⑩作業用接地取外し・最終確認　→　⑪受電所送り出し遮断器投入・DS・VCB投入【高圧復電】・常用/予備切替確認　→　⑫LBS順次投入・主幹投入【商用復旧】　→　⑬負荷・機能確認（部隊立会）・完了報告</t>
         </is>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -11028,7 +10949,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58.4" customHeight="1">
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
           <t>低圧電灯盤④</t>
@@ -11052,7 +10973,7 @@
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>1号機・2号機より各1条にて52-L二次側へ単相給電。切替時に停電が発生</t>
+          <t>1号機（52-L二次側）・2号機（特定分岐MCCB負荷側）より各1条にて単相給電。切替時に停電が発生</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11037,7 @@
     <row r="25" ht="32.2" customHeight="1">
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>※　低圧負荷の停電は、12/5　9:00頃～10:30頃（仮設切替）及び12/6　16:15頃～16:45頃（商用復旧）の切替時に限る予定。</t>
+          <t>※　低圧負荷の停電は、12/5　9:00頃～10:30頃（仮設切替）及び12/6　15:45頃～16:45頃（商用復旧）の切替時に限る予定。</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11498,14 +11419,14 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>7.1　令和8年12月4日（金）　仮設電気工事</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18.6" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>工 事 内 容</t>
         </is>
@@ -11524,7 +11445,7 @@
       <c r="I4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.6" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>作業予定時間</t>
         </is>
@@ -11543,7 +11464,7 @@
       <c r="I5" s="8" t="n"/>
     </row>
     <row r="6" ht="18.6" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>作 業 員</t>
         </is>
@@ -11562,444 +11483,444 @@
       <c r="I6" s="8" t="n"/>
     </row>
     <row r="7" ht="28.12" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>開始</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>作 業 班</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>作　業　・　業　務　項　目</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>停電</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>補　足　事　項　・　確　認　内　容</t>
         </is>
       </c>
-      <c r="H7" s="31" t="inlineStr">
+      <c r="H7" s="34" t="inlineStr">
         <is>
           <t>責任者</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="34" t="inlineStr">
         <is>
           <t>進捗確認</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28.48" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>作業前ミーティング・KY活動、保護具・測定器点検</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr"/>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr"/>
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>作業手順・作業区画の確認、指差呼称の徹底</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr"/>
+      <c r="I8" s="31" t="inlineStr"/>
     </row>
     <row r="9" ht="28.48" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>区画設置、仮設発電機　搬入・据付（1号機・2号機）</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr"/>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>区画設置、仮設発電機2台　搬入・据付</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr"/>
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>ED-02の位置に設置、水平確認、オイルパン設置</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr"/>
+      <c r="I9" s="31" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>仮設接地工事（D種）・接地抵抗測定</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr"/>
-      <c r="G10" s="33" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr"/>
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>発電機各台。100Ω以下を確認し記録</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr"/>
+      <c r="I10" s="31" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>FEP100　配管敷設（発電機～電気室）</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr"/>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>露出配管。通路横断部は防護・養生</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr"/>
+      <c r="I11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>昼休憩</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr"/>
-      <c r="G12" s="33" t="inlineStr"/>
-      <c r="H12" s="32" t="inlineStr"/>
-      <c r="I12" s="32" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr"/>
+      <c r="G12" s="30" t="inlineStr"/>
+      <c r="H12" s="31" t="inlineStr"/>
+      <c r="I12" s="31" t="inlineStr"/>
     </row>
     <row r="13" ht="28.48" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>CET150sq×6条　敷設</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr"/>
-      <c r="G13" s="33" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr"/>
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>1号機→②2条・④1条/2号機→③2条・④1条。行先表示</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr"/>
+      <c r="I13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="28.48" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>盤側端末処理・接続準備</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr"/>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr"/>
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>盤は充電中のため接続は12/5停電後。端末は絶縁処理し養生</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr"/>
+      <c r="I14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="28.48" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>発電機単体試運転・仮設ケーブル絶縁抵抗測定</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr"/>
-      <c r="G15" s="33" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr"/>
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>無負荷で電圧・周波数・相回転・単相出力を確認。0.2MΩ以上（単相回路0.1MΩ以上）</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr"/>
+      <c r="I15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="28.48" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>燃料給油・消火器配置・油流出対策</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr"/>
-      <c r="G16" s="33" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr"/>
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>吸着マット・消火器を発電機周囲に配置。貯蔵量は指定数量未満</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr"/>
+      <c r="I16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>片付け・終業点検・翌日打合せ</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr"/>
-      <c r="G17" s="33" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr"/>
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>翌日の停電手順を再確認</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr"/>
+      <c r="I17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>7.2　令和8年12月5日（土）　停電工事（1日目）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18.6" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>工 事 内 容</t>
         </is>
@@ -12018,7 +11939,7 @@
       <c r="I20" s="8" t="n"/>
     </row>
     <row r="21" ht="18.6" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>作業予定時間</t>
         </is>
@@ -12037,7 +11958,7 @@
       <c r="I21" s="8" t="n"/>
     </row>
     <row r="22" ht="18.6" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>作 業 員</t>
         </is>
@@ -12056,950 +11977,974 @@
       <c r="I22" s="8" t="n"/>
     </row>
     <row r="23" ht="28.12" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>開始</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
         <is>
           <t>作 業 班</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>作　業　・　業　務　項　目</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr">
+      <c r="F23" s="34" t="inlineStr">
         <is>
           <t>停電</t>
         </is>
       </c>
-      <c r="G23" s="31" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>補　足　事　項　・　確　認　内　容</t>
         </is>
       </c>
-      <c r="H23" s="31" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>責任者</t>
         </is>
       </c>
-      <c r="I23" s="31" t="inlineStr">
+      <c r="I23" s="34" t="inlineStr">
         <is>
           <t>進捗確認</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>作業前ミーティング・KY活動</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr"/>
-      <c r="G24" s="33" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr"/>
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>作業手順・停電範囲の確認、指差呼称の徹底</t>
         </is>
       </c>
-      <c r="H24" s="32" t="inlineStr">
+      <c r="H24" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I24" s="32" t="inlineStr"/>
+      <c r="I24" s="31" t="inlineStr"/>
     </row>
     <row r="25" ht="28.48" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>保護具・測定器・揚重機材の点検、区画設置</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr"/>
-      <c r="G25" s="33" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr"/>
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>絶縁用保護具・検電器の点検。部隊・中央監視へ停電開始を連絡</t>
         </is>
       </c>
-      <c r="H25" s="32" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I25" s="32" t="inlineStr"/>
+      <c r="I25" s="31" t="inlineStr"/>
     </row>
     <row r="26" ht="28.48" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>電気主任技術者</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>補給倉庫棟VCB（常用・予備）・LBS（89-1～3）開放　【停電開始】</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G26" s="33" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>操作禁止札設置（監督官立会）</t>
         </is>
       </c>
-      <c r="H26" s="32" t="inlineStr">
+      <c r="H26" s="31" t="inlineStr">
         <is>
           <t>足立</t>
         </is>
       </c>
-      <c r="I26" s="32" t="inlineStr"/>
+      <c r="I26" s="31" t="inlineStr"/>
     </row>
     <row r="27" ht="28.48" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>電気主任技術者
 受電所連絡員</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>受電所へ移動、送り出し遮断器（常用線・予備線）開放・施錠</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G27" s="33" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>操作禁止札設置。電気室側と無線で開放状態を相互確認</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>足立</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr"/>
-    </row>
-    <row r="28" ht="28.48" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>電気主任技術者</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>受電所から電気室へ戻り</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>移動中は無線で連絡を確保</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+      <c r="I28" s="31" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28.48" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>電気主任技術者
 ㈱アート</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>DS開放、検電・放電・作業用接地取付</t>
         </is>
       </c>
-      <c r="F28" s="32" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G28" s="33" t="inlineStr">
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>常用線・予備線とも実施。2回線の停電を全員で確認。取付位置を記録</t>
         </is>
       </c>
-      <c r="H28" s="32" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr">
         <is>
           <t>足立/中村</t>
         </is>
       </c>
-      <c r="I28" s="32" t="inlineStr"/>
-    </row>
-    <row r="29" ht="28.48" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="I29" s="31" t="inlineStr"/>
+    </row>
+    <row r="30" ht="28.48" customHeight="1">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所
 ㈱アート</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>各盤の変圧器2次導体（FBU）取外し、52-L開放（逆送防止）</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G29" s="33" t="inlineStr">
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>②③④とも実施。変圧器と低圧母線の切離しを確認し表示</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
+      <c r="H30" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr"/>
-    </row>
-    <row r="30" ht="28.48" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B30" s="32" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="I30" s="31" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40.72" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>仮設ケーブル接続（②③低圧母線　各2条・④52-L二次側　各1条）</t>
-        </is>
-      </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
+        <is>
+          <t>仮設ケーブル接続（②③低圧母線　各2条・④　1号機52-L二次側/2号機分岐MCCB負荷側）</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>相順・締付確認。④は2台が並列とならない接続であることを確認</t>
-        </is>
-      </c>
-      <c r="H30" s="32" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
+        <is>
+          <t>相順・締付確認。④の分岐MCCBは開放・施錠し2台が並列とならないことを確認</t>
+        </is>
+      </c>
+      <c r="H31" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I30" s="32" t="inlineStr"/>
-    </row>
-    <row r="31" ht="28.48" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="I31" s="31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="28.48" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
-        <is>
-          <t>発電機送電・負荷投入・機能確認　【仮設給電開始】</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>発電機送電・負荷投入　【仮設給電開始】</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G31" s="33" t="inlineStr">
+      <c r="G32" s="30" t="inlineStr">
         <is>
           <t>電圧・相回転確認、負荷を順次投入、部隊へ機能確認を依頼</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
+      <c r="H32" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I31" s="32" t="inlineStr"/>
-    </row>
-    <row r="32" ht="28.48" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="I32" s="31" t="inlineStr"/>
+    </row>
+    <row r="33" ht="28.48" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>高圧受電盤①　既設機器撤去（DS・VCB・VT・CT・継電器・計器類）</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G32" s="33" t="inlineStr">
+      <c r="G33" s="30" t="inlineStr">
         <is>
           <t>解線前にマーキング・写真記録。パネルカット部の養生</t>
         </is>
       </c>
-      <c r="H32" s="32" t="inlineStr">
+      <c r="H33" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I32" s="32" t="inlineStr"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="I33" s="31" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>各盤LBS・高圧母線（KIP）撤去</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G33" s="33" t="inlineStr">
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>解線前にマーキング・写真記録</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="H34" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I33" s="32" t="inlineStr"/>
-    </row>
-    <row r="34" ht="28.48" customHeight="1">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="I34" s="31" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28.48" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所
 ㈱アート</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>既設変圧器（T-1～T-3）一次解線、温度計配線解線、据付ボルト取外し</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G34" s="33" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>無電圧を再確認。撤去前写真</t>
         </is>
       </c>
-      <c r="H34" s="32" t="inlineStr">
+      <c r="H35" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I34" s="32" t="inlineStr"/>
-    </row>
-    <row r="35" ht="28.48" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="I35" s="31" t="inlineStr"/>
+    </row>
+    <row r="36" ht="28.48" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>既設変圧器　搬出（チェーンブロック・台車）・屋外仮置き</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G35" s="33" t="inlineStr">
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>吊り荷下立入禁止、扉・通路の養生</t>
         </is>
       </c>
-      <c r="H35" s="32" t="inlineStr">
+      <c r="H36" s="31" t="inlineStr">
         <is>
           <t>加藤</t>
         </is>
       </c>
-      <c r="I35" s="32" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="I36" s="31" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>昼休憩（発電機巡視）</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G36" s="33" t="inlineStr">
+      <c r="G37" s="30" t="inlineStr">
         <is>
           <t>発電機運転状態を確認し記録</t>
         </is>
       </c>
-      <c r="H36" s="32" t="inlineStr">
+      <c r="H37" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I36" s="32" t="inlineStr"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="I37" s="31" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E37" s="33" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>変圧器架台据付（②③④）</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G37" s="33" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>水平・アンカー・締付トルク記録</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I37" s="32" t="inlineStr"/>
-    </row>
-    <row r="38" ht="40.72" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="I38" s="31" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28.12" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>作 業 班</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>作　業　・　業　務　項　目</t>
+        </is>
+      </c>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t>停電</t>
+        </is>
+      </c>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>補　足　事　項　・　確　認　内　容</t>
+        </is>
+      </c>
+      <c r="H39" s="34" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
+      <c r="I39" s="34" t="inlineStr">
+        <is>
+          <t>進捗確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40.72" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>新設変圧器　搬入・据付（T-1　1,140kg・T-2　540kg・T-3　440kg）</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G38" s="33" t="inlineStr">
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>2tユニックで荷下ろし後、台車・チェーンブロックで据付。つり耳使用、吊り角度60度以内。防振ゴム設置・水平確認</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="H40" s="31" t="inlineStr">
         <is>
           <t>加藤</t>
         </is>
       </c>
-      <c r="I38" s="32" t="inlineStr"/>
-    </row>
-    <row r="39" ht="28.12" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>作 業 班</t>
-        </is>
-      </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>作　業　・　業　務　項　目</t>
-        </is>
-      </c>
-      <c r="F39" s="31" t="inlineStr">
-        <is>
-          <t>停電</t>
-        </is>
-      </c>
-      <c r="G39" s="31" t="inlineStr">
-        <is>
-          <t>補　足　事　項　・　確　認　内　容</t>
-        </is>
-      </c>
-      <c r="H39" s="31" t="inlineStr">
-        <is>
-          <t>責任者</t>
-        </is>
-      </c>
-      <c r="I39" s="31" t="inlineStr">
-        <is>
-          <t>進捗確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28.48" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="I40" s="31" t="inlineStr"/>
+    </row>
+    <row r="41" ht="28.48" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>高圧受電盤①　新設機器取付（VCB取付プレート・DS・VT・CT等）</t>
         </is>
       </c>
-      <c r="F40" s="32" t="inlineStr">
+      <c r="F41" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G40" s="33" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>承諾図との照合、締付トルク記録</t>
         </is>
       </c>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="H41" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I40" s="32" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="I41" s="31" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E41" s="33" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>盤内清掃・養生、発電機運転状態確認・給油</t>
         </is>
       </c>
-      <c r="F41" s="32" t="inlineStr">
+      <c r="F42" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G41" s="33" t="inlineStr">
+      <c r="G42" s="30" t="inlineStr">
         <is>
           <t>燃料残量・油漏れ確認、運転記録へ記入</t>
         </is>
       </c>
-      <c r="H41" s="32" t="inlineStr">
+      <c r="H42" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I41" s="32" t="inlineStr"/>
-    </row>
-    <row r="42" ht="28.48" customHeight="1">
-      <c r="A42" s="32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="I42" s="31" t="inlineStr"/>
+    </row>
+    <row r="43" ht="28.48" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="D43" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E42" s="33" t="inlineStr">
+      <c r="E43" s="30" t="inlineStr">
         <is>
           <t>終業点検・片付け・報告、夜間監視体制への引継ぎ</t>
         </is>
       </c>
-      <c r="F42" s="32" t="inlineStr">
+      <c r="F43" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G42" s="33" t="inlineStr">
+      <c r="G43" s="30" t="inlineStr">
         <is>
           <t>工具残置確認。作業用接地は取付のまま継続。夜間監視員へ引継ぎ</t>
         </is>
       </c>
-      <c r="H42" s="32" t="inlineStr">
+      <c r="H43" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I42" s="32" t="inlineStr"/>
-    </row>
-    <row r="43" ht="28.48" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="I43" s="31" t="inlineStr"/>
+    </row>
+    <row r="44" ht="28.48" customHeight="1">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="C44" s="31" t="inlineStr">
         <is>
           <t>翌08:30</t>
         </is>
       </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="D44" s="31" t="inlineStr">
         <is>
           <t>夜間監視員</t>
         </is>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>仮設発電機　夜間連続運転・監視</t>
         </is>
       </c>
-      <c r="F43" s="32" t="inlineStr">
+      <c r="F44" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G43" s="33" t="inlineStr">
+      <c r="G44" s="30" t="inlineStr">
         <is>
           <t>2時間毎に電圧・電流・周波数・燃料残量を記録。異常時は作業指揮者へ連絡</t>
         </is>
       </c>
-      <c r="H43" s="32" t="inlineStr">
+      <c r="H44" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I43" s="32" t="inlineStr"/>
-    </row>
-    <row r="44" ht="10" customHeight="1"/>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="I44" s="31" t="inlineStr"/>
+    </row>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>7.3　令和8年12月6日（日）　停電工事（2日目）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18.6" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
+    <row r="47" ht="18.6" customHeight="1">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>工 事 内 容</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>新設機器の取付・結線、高圧母線張替え、試験・検査及び復電（当日復電）</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="8" t="n"/>
-    </row>
-    <row r="47" ht="18.6" customHeight="1">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>作業予定時間</t>
         </is>
       </c>
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="26" t="inlineStr">
         <is>
-          <t>9:00　～　17:00頃　（作業前ミーティング8:30～/試験・検査終了後に復電、商用切替・負荷確認を含め17:00頃終了予定）</t>
+          <t>新設機器の取付・結線、高圧母線張替え、試験・検査及び復電（当日復電）</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -13009,16 +12954,16 @@
       <c r="I47" s="8" t="n"/>
     </row>
     <row r="48" ht="18.6" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>作 業 員</t>
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>作業予定時間</t>
         </is>
       </c>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t>㈱アート3名　/　別川製作所6名　/　ARワーク5名　/　関西テクノ1名　/　電気主任技術者1名　/　関西電気保安協会2名　（計18名）</t>
+          <t>9:00　～　17:00頃　（作業前ミーティング8:30～/試験・検査終了後に復電、商用切替・負荷確認を含め17:00頃終了予定）</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -13027,920 +12972,944 @@
       <c r="H48" s="10" t="n"/>
       <c r="I48" s="8" t="n"/>
     </row>
-    <row r="49" ht="28.12" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+    <row r="49" ht="18.6" customHeight="1">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>作 業 員</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>㈱アート3名　/　別川製作所6名　/　ARワーク5名　/　関西テクノ1名　/　電気主任技術者1名　/　関西電気保安協会2名　（計18名）</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="28.12" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B49" s="31" t="inlineStr">
+      <c r="B50" s="34" t="inlineStr">
         <is>
           <t>開始</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="D49" s="31" t="inlineStr">
+      <c r="D50" s="34" t="inlineStr">
         <is>
           <t>作 業 班</t>
         </is>
       </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="E50" s="34" t="inlineStr">
         <is>
           <t>作　業　・　業　務　項　目</t>
         </is>
       </c>
-      <c r="F49" s="31" t="inlineStr">
+      <c r="F50" s="34" t="inlineStr">
         <is>
           <t>停電</t>
         </is>
       </c>
-      <c r="G49" s="31" t="inlineStr">
+      <c r="G50" s="34" t="inlineStr">
         <is>
           <t>補　足　事　項　・　確　認　内　容</t>
         </is>
       </c>
-      <c r="H49" s="31" t="inlineStr">
+      <c r="H50" s="34" t="inlineStr">
         <is>
           <t>責任者</t>
         </is>
       </c>
-      <c r="I49" s="31" t="inlineStr">
+      <c r="I50" s="34" t="inlineStr">
         <is>
           <t>進捗確認</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="32" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
+      <c r="C51" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D50" s="32" t="inlineStr">
+      <c r="D51" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E50" s="33" t="inlineStr">
+      <c r="E51" s="30" t="inlineStr">
         <is>
           <t>作業前ミーティング・KY活動</t>
         </is>
       </c>
-      <c r="F50" s="32" t="inlineStr">
+      <c r="F51" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G50" s="33" t="inlineStr">
+      <c r="G51" s="30" t="inlineStr">
         <is>
           <t>夜間の発電機運転記録確認、当日手順の確認</t>
         </is>
       </c>
-      <c r="H50" s="32" t="inlineStr">
+      <c r="H51" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I50" s="32" t="inlineStr"/>
-    </row>
-    <row r="51" ht="28.48" customHeight="1">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="I51" s="31" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28.48" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="D52" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E51" s="33" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>作業用接地の取付状況確認・保護具点検</t>
         </is>
       </c>
-      <c r="F51" s="32" t="inlineStr">
+      <c r="F52" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G51" s="33" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>前日からの継続取付を全員で確認</t>
         </is>
       </c>
-      <c r="H51" s="32" t="inlineStr">
+      <c r="H52" s="31" t="inlineStr">
         <is>
           <t>足立/中村</t>
         </is>
       </c>
-      <c r="I51" s="32" t="inlineStr"/>
-    </row>
-    <row r="52" ht="28.48" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="I52" s="31" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28.48" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="D53" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E52" s="33" t="inlineStr">
+      <c r="E53" s="30" t="inlineStr">
         <is>
           <t>高圧受電盤①　新設機器結線（主回路・制御配線・テスト端子・CTD・MCCB）</t>
         </is>
       </c>
-      <c r="F52" s="32" t="inlineStr">
+      <c r="F53" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G52" s="33" t="inlineStr">
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>相順確認、増締めチェックマーク表示</t>
         </is>
       </c>
-      <c r="H52" s="32" t="inlineStr">
+      <c r="H53" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I52" s="32" t="inlineStr"/>
-    </row>
-    <row r="53" ht="28.48" customHeight="1">
-      <c r="A53" s="32" t="inlineStr">
+      <c r="I53" s="31" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28.48" customHeight="1">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="C54" s="31" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="D54" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E53" s="33" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>各盤　新設LBS（PF　G50A・G30A・G40A）取付、高圧母線（KIP）張替え</t>
         </is>
       </c>
-      <c r="F53" s="32" t="inlineStr">
+      <c r="F54" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G53" s="33" t="inlineStr">
+      <c r="G54" s="30" t="inlineStr">
         <is>
           <t>相順確認、締付トルク記録</t>
         </is>
       </c>
-      <c r="H53" s="32" t="inlineStr">
+      <c r="H54" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I53" s="32" t="inlineStr"/>
-    </row>
-    <row r="54" ht="28.48" customHeight="1">
-      <c r="A54" s="32" t="inlineStr">
+      <c r="I54" s="31" t="inlineStr"/>
+    </row>
+    <row r="55" ht="28.48" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C54" s="32" t="inlineStr">
+      <c r="C55" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="D55" s="31" t="inlineStr">
         <is>
           <t>ARワーク㈱</t>
         </is>
       </c>
-      <c r="E54" s="33" t="inlineStr">
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>変圧器　据付位置最終調整・固定、撤去変圧器の積込・搬出</t>
         </is>
       </c>
-      <c r="F54" s="32" t="inlineStr">
+      <c r="F55" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G54" s="33" t="inlineStr">
+      <c r="G55" s="30" t="inlineStr">
         <is>
           <t>防振ゴム位置確認。積込は2tユニック車の積載量内で複数回に分ける</t>
         </is>
       </c>
-      <c r="H54" s="32" t="inlineStr">
+      <c r="H55" s="31" t="inlineStr">
         <is>
           <t>加藤</t>
         </is>
       </c>
-      <c r="I54" s="32" t="inlineStr"/>
-    </row>
-    <row r="55" ht="40.72" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="I55" s="31" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40.72" customHeight="1">
+      <c r="A56" s="31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B55" s="32" t="inlineStr">
+      <c r="B56" s="31" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="C55" s="32" t="inlineStr">
+      <c r="C56" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D56" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所
 ㈱アート</t>
         </is>
       </c>
-      <c r="E55" s="33" t="inlineStr">
+      <c r="E56" s="30" t="inlineStr">
         <is>
           <t>変圧器一次結線、新設2次導体の変圧器側結線、タップ設定、ダイヤル温度計配線</t>
         </is>
       </c>
-      <c r="F55" s="32" t="inlineStr">
+      <c r="F56" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G55" s="33" t="inlineStr">
+      <c r="G56" s="30" t="inlineStr">
         <is>
           <t>2次導体の母線側は接続せず絶縁養生（発電機切離し後に接続）。タップ位置（R6600V標準）・締付トルク記録</t>
         </is>
       </c>
-      <c r="H55" s="32" t="inlineStr">
+      <c r="H56" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I55" s="32" t="inlineStr"/>
-    </row>
-    <row r="56" ht="28.48" customHeight="1">
-      <c r="A56" s="32" t="inlineStr">
+      <c r="I56" s="31" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28.48" customHeight="1">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B57" s="31" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
+      <c r="C57" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="D57" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所</t>
         </is>
       </c>
-      <c r="E56" s="33" t="inlineStr">
+      <c r="E57" s="30" t="inlineStr">
         <is>
           <t>低圧電灯盤④　CT（L）×2・THR・MDA×2取替え</t>
         </is>
       </c>
-      <c r="F56" s="32" t="inlineStr">
+      <c r="F57" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G56" s="33" t="inlineStr">
+      <c r="G57" s="30" t="inlineStr">
         <is>
           <t>④の仮設給電は52-L二次側のため主幹回路は無電圧。検電のうえ実施</t>
         </is>
       </c>
-      <c r="H56" s="32" t="inlineStr">
+      <c r="H57" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I56" s="32" t="inlineStr"/>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="I57" s="31" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B57" s="32" t="inlineStr">
+      <c r="B58" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
+      <c r="C58" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D58" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E57" s="33" t="inlineStr">
+      <c r="E58" s="30" t="inlineStr">
         <is>
           <t>昼休憩（発電機巡視）</t>
         </is>
       </c>
-      <c r="F57" s="32" t="inlineStr">
+      <c r="F58" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G57" s="33" t="inlineStr">
+      <c r="G58" s="30" t="inlineStr">
         <is>
           <t>発電機運転状態を確認し記録</t>
         </is>
       </c>
-      <c r="H57" s="32" t="inlineStr">
+      <c r="H58" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I57" s="32" t="inlineStr"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="32" t="inlineStr">
+      <c r="I58" s="31" t="inlineStr"/>
+    </row>
+    <row r="59" ht="28.12" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>作 業 班</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>作　業　・　業　務　項　目</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>停電</t>
+        </is>
+      </c>
+      <c r="G59" s="34" t="inlineStr">
+        <is>
+          <t>補　足　事　項　・　確　認　内　容</t>
+        </is>
+      </c>
+      <c r="H59" s="34" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
+      <c r="I59" s="34" t="inlineStr">
+        <is>
+          <t>進捗確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
+      <c r="C60" s="31" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="D60" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E58" s="33" t="inlineStr">
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>接地線接続（EA・EB・ED）、盤内清掃</t>
         </is>
       </c>
-      <c r="F58" s="32" t="inlineStr">
+      <c r="F60" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G58" s="33" t="inlineStr">
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>接地端子の締付確認、工具残置確認</t>
         </is>
       </c>
-      <c r="H58" s="32" t="inlineStr">
+      <c r="H60" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I58" s="32" t="inlineStr"/>
-    </row>
-    <row r="59" ht="28.48" customHeight="1">
-      <c r="A59" s="32" t="inlineStr">
+      <c r="I60" s="31" t="inlineStr"/>
+    </row>
+    <row r="61" ht="28.48" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B59" s="32" t="inlineStr">
+      <c r="B61" s="31" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="D61" s="31" t="inlineStr">
         <is>
           <t>㈱別川製作所
 ㈱アート</t>
         </is>
       </c>
-      <c r="E59" s="33" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>自主試験（絶縁抵抗・接地抵抗・シーケンス・インターロック）</t>
         </is>
       </c>
-      <c r="F59" s="32" t="inlineStr">
+      <c r="F61" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G59" s="33" t="inlineStr">
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>VCB投入・引外し、常用/予備インターロック確認。測定記録へ記入</t>
         </is>
       </c>
-      <c r="H59" s="32" t="inlineStr">
+      <c r="H61" s="31" t="inlineStr">
         <is>
           <t>島津</t>
         </is>
       </c>
-      <c r="I59" s="32" t="inlineStr"/>
-    </row>
-    <row r="60" ht="28.12" customHeight="1">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="C60" s="31" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="D60" s="31" t="inlineStr">
-        <is>
-          <t>作 業 班</t>
-        </is>
-      </c>
-      <c r="E60" s="31" t="inlineStr">
-        <is>
-          <t>作　業　・　業　務　項　目</t>
-        </is>
-      </c>
-      <c r="F60" s="31" t="inlineStr">
-        <is>
-          <t>停電</t>
-        </is>
-      </c>
-      <c r="G60" s="31" t="inlineStr">
-        <is>
-          <t>補　足　事　項　・　確　認　内　容</t>
-        </is>
-      </c>
-      <c r="H60" s="31" t="inlineStr">
-        <is>
-          <t>責任者</t>
-        </is>
-      </c>
-      <c r="I60" s="31" t="inlineStr">
-        <is>
-          <t>進捗確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28.48" customHeight="1">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="I61" s="31" t="inlineStr"/>
+    </row>
+    <row r="62" ht="28.48" customHeight="1">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="C61" s="32" t="inlineStr">
+      <c r="C62" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="D62" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E61" s="33" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>試験準備・盤内最終確認</t>
         </is>
       </c>
-      <c r="F61" s="32" t="inlineStr">
+      <c r="F62" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G61" s="33" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>試験区画の設定、工具・材料の残置確認（指差呼称）</t>
         </is>
       </c>
-      <c r="H61" s="32" t="inlineStr">
+      <c r="H62" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I61" s="32" t="inlineStr"/>
-    </row>
-    <row r="62" ht="40.72" customHeight="1">
-      <c r="A62" s="32" t="inlineStr">
+      <c r="I62" s="31" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40.72" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B62" s="32" t="inlineStr">
+      <c r="B63" s="31" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="inlineStr">
         <is>
           <t>関西電気保安協会
 ㈱アート</t>
         </is>
       </c>
-      <c r="E62" s="33" t="inlineStr">
+      <c r="E63" s="30" t="inlineStr">
         <is>
           <t>試験・検査（絶縁抵抗・絶縁耐力・保護継電器（OCR・UVR）・受電前検査）</t>
         </is>
       </c>
-      <c r="F62" s="32" t="inlineStr">
+      <c r="F63" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G62" s="33" t="inlineStr">
+      <c r="G63" s="30" t="inlineStr">
         <is>
           <t>作業用接地は電気主任技術者の指示で一時取外し・再取付（記録）。試験区画は立入禁止。監督官の確認を受ける</t>
         </is>
       </c>
-      <c r="H62" s="32" t="inlineStr">
+      <c r="H63" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I62" s="32" t="inlineStr"/>
-    </row>
-    <row r="63" ht="28.48" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
+      <c r="I63" s="31" t="inlineStr"/>
+    </row>
+    <row r="64" ht="28.48" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B63" s="32" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="D64" s="31" t="inlineStr">
+        <is>
+          <t>㈱アート
+㈱別川製作所</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>発電機停止・仮設ケーブル切離し、低圧母線絶縁抵抗測定、2次導体母線側接続</t>
+        </is>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G64" s="30" t="inlineStr">
+        <is>
+          <t>高圧停電・作業用接地中に実施【低圧停電】。締付トルク記録</t>
+        </is>
+      </c>
+      <c r="H64" s="31" t="inlineStr">
+        <is>
+          <t>中村</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr"/>
+    </row>
+    <row r="65" ht="28.48" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E63" s="33" t="inlineStr">
+      <c r="E65" s="30" t="inlineStr">
         <is>
           <t>作業用接地取外し・最終確認</t>
         </is>
       </c>
-      <c r="F63" s="32" t="inlineStr">
+      <c r="F65" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G63" s="33" t="inlineStr">
+      <c r="G65" s="30" t="inlineStr">
         <is>
           <t>取外し数量の照合、全員集合のうえ確認</t>
         </is>
       </c>
-      <c r="H63" s="32" t="inlineStr">
+      <c r="H65" s="31" t="inlineStr">
         <is>
           <t>足立/中村</t>
         </is>
       </c>
-      <c r="I63" s="32" t="inlineStr"/>
-    </row>
-    <row r="64" ht="28.48" customHeight="1">
-      <c r="A64" s="32" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B64" s="32" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="I65" s="31" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28.48" customHeight="1">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="D66" s="31" t="inlineStr">
         <is>
           <t>電気主任技術者
 受電所連絡員</t>
         </is>
       </c>
-      <c r="E64" s="33" t="inlineStr">
-        <is>
-          <t>受電所送り出し遮断器（常用線・予備線）投入、常用DS・VCB投入　【高圧復電】</t>
-        </is>
-      </c>
-      <c r="F64" s="32" t="inlineStr">
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>受電所へ移動、送り出し遮断器（常用線・予備線）投入</t>
+        </is>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G64" s="33" t="inlineStr">
-        <is>
-          <t>LBSは開放のまま。操作禁止札撤去、復電の全員周知、電圧確認</t>
-        </is>
-      </c>
-      <c r="H64" s="32" t="inlineStr">
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>操作禁止札・施錠撤去。電気室側と無線で相互確認</t>
+        </is>
+      </c>
+      <c r="H66" s="31" t="inlineStr">
         <is>
           <t>足立</t>
         </is>
       </c>
-      <c r="I64" s="32" t="inlineStr"/>
-    </row>
-    <row r="65" ht="28.48" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B65" s="32" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="I66" s="31" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28.48" customHeight="1">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="inlineStr">
+        <is>
+          <t>電気主任技術者</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>電気室へ戻り、常用DS・VCB投入　【高圧復電】</t>
+        </is>
+      </c>
+      <c r="F67" s="31" t="inlineStr"/>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>LBSは開放のまま。復電を全員周知、電圧確認</t>
+        </is>
+      </c>
+      <c r="H67" s="31" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28.48" customHeight="1">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="inlineStr">
         <is>
           <t>電気主任技術者
 ㈱別川製作所</t>
         </is>
       </c>
-      <c r="E65" s="33" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>常用/予備切替動作確認・相回転確認</t>
         </is>
       </c>
-      <c r="F65" s="32" t="inlineStr"/>
-      <c r="G65" s="33" t="inlineStr">
-        <is>
-          <t>予備線はDS投入・VCB開放の待機状態とする。両回線の相回転一致を確認</t>
-        </is>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
+      <c r="F68" s="31" t="inlineStr"/>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>予備線はDS投入・VCB開放の待機状態とする</t>
+        </is>
+      </c>
+      <c r="H68" s="31" t="inlineStr">
         <is>
           <t>足立</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr"/>
-    </row>
-    <row r="66" ht="28.48" customHeight="1">
-      <c r="A66" s="32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C66" s="32" t="inlineStr">
+      <c r="I68" s="31" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28.48" customHeight="1">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
         <is>
           <t>16:35</t>
         </is>
       </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>㈱アート
-㈱別川製作所</t>
-        </is>
-      </c>
-      <c r="E66" s="33" t="inlineStr">
-        <is>
-          <t>発電機停止・仮設ケーブル切離し、新設2次導体の母線側接続</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr"/>
-      <c r="G66" s="33" t="inlineStr">
-        <is>
-          <t>発電機と商用が同時接続されないことを確認。締付トルク記録</t>
-        </is>
-      </c>
-      <c r="H66" s="32" t="inlineStr">
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>電気主任技術者</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>LBS（89-1～3）順次投入、主幹投入　【商用復旧】</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr"/>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>変圧器の異音・励磁状態を確認。電圧・相回転測定。盤扉閉・充電部への接近禁止</t>
+        </is>
+      </c>
+      <c r="H69" s="31" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+    </row>
+    <row r="70" ht="28.48" customHeight="1">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>負荷復旧・機能確認、最終確認・完了報告</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr"/>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>MCCBを順次投入、部隊立会のもと機能確認。監督官・部隊へ完了報告</t>
+        </is>
+      </c>
+      <c r="H70" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I66" s="32" t="inlineStr"/>
-    </row>
-    <row r="67" ht="28.48" customHeight="1">
-      <c r="A67" s="32" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>電気主任技術者</t>
-        </is>
-      </c>
-      <c r="E67" s="33" t="inlineStr">
-        <is>
-          <t>LBS（89-1～3）順次投入、主幹投入　【商用復旧】</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr"/>
-      <c r="G67" s="33" t="inlineStr">
-        <is>
-          <t>変圧器の異音・励磁状態を確認。電圧・相回転測定</t>
-        </is>
-      </c>
-      <c r="H67" s="32" t="inlineStr">
-        <is>
-          <t>足立</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-    </row>
-    <row r="68" ht="28.48" customHeight="1">
-      <c r="A68" s="32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C68" s="32" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="E68" s="33" t="inlineStr">
-        <is>
-          <t>負荷復旧・機能確認、最終確認・完了報告</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr"/>
-      <c r="G68" s="33" t="inlineStr">
-        <is>
-          <t>MCCBを順次投入、部隊立会のもと機能確認。監督官・部隊へ完了報告</t>
-        </is>
-      </c>
-      <c r="H68" s="32" t="inlineStr">
-        <is>
-          <t>中村</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="I70" s="31" t="inlineStr"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="32" t="inlineStr">
         <is>
           <t>7.4　令和8年12月7日（月）　仮設撤去工事</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="18.6" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72" ht="18.6" customHeight="1">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>工 事 内 容</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="26" t="inlineStr">
-        <is>
-          <t>仮設発電機・仮設配管配線の撤去及び原状復旧（停電なし）</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="8" t="n"/>
-    </row>
-    <row r="71" ht="18.6" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>作業予定時間</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="8" t="n"/>
-      <c r="D71" s="26" t="inlineStr">
-        <is>
-          <t>9:00　～　16:00　（作業前ミーティング　8:45～）</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="8" t="n"/>
-    </row>
-    <row r="72" ht="18.6" customHeight="1">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>作 業 員</t>
         </is>
       </c>
       <c r="B72" s="10" t="n"/>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="26" t="inlineStr">
         <is>
-          <t>㈱アート4名（作業指揮者を含む）</t>
+          <t>仮設発電機・仮設配管配線の撤去及び原状復旧（停電なし）</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
@@ -13949,384 +13918,422 @@
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="8" t="n"/>
     </row>
-    <row r="73" ht="28.12" customHeight="1">
-      <c r="A73" s="31" t="inlineStr">
+    <row r="73" ht="18.6" customHeight="1">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>作業予定時間</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>9:00　～　16:00　（作業前ミーティング　8:45～）</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="8" t="n"/>
+    </row>
+    <row r="74" ht="18.6" customHeight="1">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>作 業 員</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>㈱アート4名（作業指揮者を含む）</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="8" t="n"/>
+    </row>
+    <row r="75" ht="28.12" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B73" s="31" t="inlineStr">
+      <c r="B75" s="34" t="inlineStr">
         <is>
           <t>開始</t>
         </is>
       </c>
-      <c r="C73" s="31" t="inlineStr">
+      <c r="C75" s="34" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="D73" s="31" t="inlineStr">
+      <c r="D75" s="34" t="inlineStr">
         <is>
           <t>作 業 班</t>
         </is>
       </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="E75" s="34" t="inlineStr">
         <is>
           <t>作　業　・　業　務　項　目</t>
         </is>
       </c>
-      <c r="F73" s="31" t="inlineStr">
+      <c r="F75" s="34" t="inlineStr">
         <is>
           <t>停電</t>
         </is>
       </c>
-      <c r="G73" s="31" t="inlineStr">
+      <c r="G75" s="34" t="inlineStr">
         <is>
           <t>補　足　事　項　・　確　認　内　容</t>
         </is>
       </c>
-      <c r="H73" s="31" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>責任者</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr">
+      <c r="I75" s="34" t="inlineStr">
         <is>
           <t>進捗確認</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="28.48" customHeight="1">
-      <c r="A74" s="32" t="inlineStr">
+    <row r="76" ht="28.48" customHeight="1">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B74" s="32" t="inlineStr">
+      <c r="B76" s="31" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="C74" s="32" t="inlineStr">
+      <c r="C76" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="D76" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E74" s="33" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>作業前ミーティング・KY活動、保護具・工具点検</t>
         </is>
       </c>
-      <c r="F74" s="32" t="inlineStr"/>
-      <c r="G74" s="33" t="inlineStr">
+      <c r="F76" s="31" t="inlineStr"/>
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>撤去手順・作業区画の確認</t>
         </is>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H76" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-    </row>
-    <row r="75" ht="28.48" customHeight="1">
-      <c r="A75" s="32" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr"/>
+    </row>
+    <row r="77" ht="28.48" customHeight="1">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B75" s="32" t="inlineStr">
+      <c r="B77" s="31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C75" s="32" t="inlineStr">
+      <c r="C77" s="31" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="D77" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E75" s="33" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>区画設置、仮設ケーブル盤側端末の撤去確認</t>
         </is>
       </c>
-      <c r="F75" s="32" t="inlineStr"/>
-      <c r="G75" s="33" t="inlineStr">
+      <c r="F77" s="31" t="inlineStr"/>
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>盤側は12/6に切離し済み。盤内の絶縁・残置物を確認</t>
         </is>
       </c>
-      <c r="H75" s="32" t="inlineStr">
+      <c r="H77" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr"/>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="32" t="inlineStr">
+      <c r="I77" s="31" t="inlineStr"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B76" s="32" t="inlineStr">
+      <c r="B78" s="31" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
+      <c r="C78" s="31" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D76" s="32" t="inlineStr">
+      <c r="D78" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E76" s="33" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>CET150sq×6条・FEP100　撤去</t>
         </is>
       </c>
-      <c r="F76" s="32" t="inlineStr"/>
-      <c r="G76" s="33" t="inlineStr">
+      <c r="F78" s="31" t="inlineStr"/>
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>撤去品の分別・整理</t>
         </is>
       </c>
-      <c r="H76" s="32" t="inlineStr">
+      <c r="H78" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I76" s="32" t="inlineStr"/>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="32" t="inlineStr">
+      <c r="I78" s="31" t="inlineStr"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B77" s="32" t="inlineStr">
+      <c r="B79" s="31" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C79" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="D79" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E77" s="33" t="inlineStr">
+      <c r="E79" s="30" t="inlineStr">
         <is>
           <t>仮設接地撤去</t>
         </is>
       </c>
-      <c r="F77" s="32" t="inlineStr"/>
-      <c r="G77" s="33" t="inlineStr"/>
-      <c r="H77" s="32" t="inlineStr">
+      <c r="F79" s="31" t="inlineStr"/>
+      <c r="G79" s="30" t="inlineStr"/>
+      <c r="H79" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="32" t="inlineStr">
+      <c r="I79" s="31" t="inlineStr"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B80" s="31" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="C80" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="D80" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E78" s="33" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>昼休憩</t>
         </is>
       </c>
-      <c r="F78" s="32" t="inlineStr"/>
-      <c r="G78" s="33" t="inlineStr"/>
-      <c r="H78" s="32" t="inlineStr"/>
-      <c r="I78" s="32" t="inlineStr"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="32" t="inlineStr">
+      <c r="F80" s="31" t="inlineStr"/>
+      <c r="G80" s="30" t="inlineStr"/>
+      <c r="H80" s="31" t="inlineStr"/>
+      <c r="I80" s="31" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="B81" s="31" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C81" s="31" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D81" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E79" s="33" t="inlineStr">
+      <c r="E81" s="30" t="inlineStr">
         <is>
           <t>仮設発電機　搬出</t>
         </is>
       </c>
-      <c r="F79" s="32" t="inlineStr"/>
-      <c r="G79" s="33" t="inlineStr">
+      <c r="F81" s="31" t="inlineStr"/>
+      <c r="G81" s="30" t="inlineStr">
         <is>
           <t>燃料残量・油漏れの確認</t>
         </is>
       </c>
-      <c r="H79" s="32" t="inlineStr">
+      <c r="H81" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="32" t="inlineStr">
+      <c r="I81" s="31" t="inlineStr"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B80" s="32" t="inlineStr">
+      <c r="B82" s="31" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
+      <c r="C82" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="D82" s="31" t="inlineStr">
         <is>
           <t>㈱アート</t>
         </is>
       </c>
-      <c r="E80" s="33" t="inlineStr">
+      <c r="E82" s="30" t="inlineStr">
         <is>
           <t>原状復旧・清掃、オイルパン・吸着マット撤去</t>
         </is>
       </c>
-      <c r="F80" s="32" t="inlineStr"/>
-      <c r="G80" s="33" t="inlineStr">
+      <c r="F82" s="31" t="inlineStr"/>
+      <c r="G82" s="30" t="inlineStr">
         <is>
           <t>設置場所の損傷・油染みの有無を確認</t>
         </is>
       </c>
-      <c r="H80" s="32" t="inlineStr">
+      <c r="H82" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-    </row>
-    <row r="81" ht="28.48" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
+      <c r="I82" s="31" t="inlineStr"/>
+    </row>
+    <row r="83" ht="28.48" customHeight="1">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B81" s="32" t="inlineStr">
+      <c r="B83" s="31" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D83" s="31" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E81" s="33" t="inlineStr">
+      <c r="E83" s="30" t="inlineStr">
         <is>
           <t>新設変圧器の運転状態確認・完了報告</t>
         </is>
       </c>
-      <c r="F81" s="32" t="inlineStr"/>
-      <c r="G81" s="33" t="inlineStr">
+      <c r="F83" s="31" t="inlineStr"/>
+      <c r="G83" s="30" t="inlineStr">
         <is>
           <t>温度・異音・電圧を確認し記録。監督官・部隊へ報告</t>
         </is>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H83" s="31" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
+      <c r="I83" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D70:I70"/>
+    <mergeCell ref="D49:I49"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D48:I48"/>
     <mergeCell ref="D72:I72"/>
     <mergeCell ref="D47:I47"/>
-    <mergeCell ref="A71:C71"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D71:I71"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D74:I74"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A72:C72"/>
+    <mergeCell ref="D73:I73"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A70:C70"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="A69:I69"/>
     <mergeCell ref="D21:I21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -14343,8 +14350,8 @@
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="18" min="0" max="16383" man="1"/>
     <brk id="38" min="0" max="16383" man="1"/>
-    <brk id="59" min="0" max="16383" man="1"/>
-    <brk id="68" min="0" max="16383" man="1"/>
+    <brk id="58" min="0" max="16383" man="1"/>
+    <brk id="70" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -14381,12 +14388,12 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>【ED-02　仮設工事（補給倉庫棟部分）】</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>【ED-08　補給倉庫棟　平面図（電気室部分）】</t>
         </is>
@@ -14460,7 +14467,7 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>【ED-10　補給倉庫棟　単線結線図　改修後　―　改修範囲（太線部）を赤色で表示/縮小図のため詳細は原図（A3）による】</t>
         </is>
@@ -14547,23 +14554,23 @@
       </c>
     </row>
     <row r="50" ht="19.28" customHeight="1">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>区　分</t>
         </is>
       </c>
-      <c r="B50" s="35" t="inlineStr">
+      <c r="B50" s="36" t="inlineStr">
         <is>
           <t>内　　容</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
-      <c r="D50" s="35" t="inlineStr">
+      <c r="D50" s="36" t="inlineStr">
         <is>
           <t>仕　様　・　数　量</t>
         </is>
       </c>
-      <c r="E50" s="35" t="inlineStr">
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t>備　　考</t>
         </is>
@@ -14571,7 +14578,7 @@
       <c r="F50" s="8" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>仮設電源</t>
         </is>
@@ -14582,7 +14589,7 @@
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
-      <c r="D51" s="36" t="inlineStr">
+      <c r="D51" s="37" t="inlineStr">
         <is>
           <t>400kVA×2台</t>
         </is>
@@ -14595,7 +14602,7 @@
       <c r="F51" s="8" t="n"/>
     </row>
     <row r="52" ht="32.56" customHeight="1">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>仮設配線</t>
         </is>
@@ -14607,7 +14614,7 @@
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
-      <c r="D52" s="36" t="inlineStr">
+      <c r="D52" s="37" t="inlineStr">
         <is>
           <t>6条</t>
         </is>
@@ -14620,8 +14627,8 @@
       </c>
       <c r="F52" s="8" t="n"/>
     </row>
-    <row r="53" ht="32.56" customHeight="1">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="53" ht="46.84" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>接続点</t>
         </is>
@@ -14629,24 +14636,24 @@
       <c r="B53" s="9" t="inlineStr">
         <is>
           <t>②③:低圧母線（FBU負荷側）
-④:52-L二次側（分岐母線）</t>
+④:1号機は52-L二次側、2号機は特定分岐MCCB負荷側（MCCB開放・施錠）</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
-      <c r="D53" s="36" t="inlineStr">
+      <c r="D53" s="37" t="inlineStr">
         <is>
           <t>②③④</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>変圧器2次導体（FBU）取外しにより逆送防止。④は2台の発電機が並列とならない接続とする</t>
+          <t>変圧器2次導体（FBU）取外しにより逆送防止。④は2台が並列とならない</t>
         </is>
       </c>
       <c r="F53" s="8" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>仮設接地</t>
         </is>
@@ -14657,7 +14664,7 @@
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
-      <c r="D54" s="36" t="inlineStr">
+      <c r="D54" s="37" t="inlineStr">
         <is>
           <t>D種　100Ω以下</t>
         </is>
@@ -14670,7 +14677,7 @@
       <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="46.84" customHeight="1">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>燃　料</t>
         </is>
@@ -14681,21 +14688,22 @@
         </is>
       </c>
       <c r="C55" s="8" t="n"/>
-      <c r="D55" s="36" t="inlineStr">
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>6,758.4L
-（24h×2日×2台×70.4L/h）</t>
+（24h×2日×2台
+×70.4L/h）</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>分割補給とし現場貯蔵は指定数量（1,000L）未満。超える場合は消防署へ仮貯蔵承認申請</t>
+          <t>分割補給とし現場貯蔵は指定数量（1,000L）未満。200L以上は少量危険物の届出</t>
         </is>
       </c>
       <c r="F55" s="8" t="n"/>
     </row>
     <row r="56" ht="32.56" customHeight="1">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>揚重機械</t>
         </is>
@@ -14706,7 +14714,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
-      <c r="D56" s="36" t="inlineStr">
+      <c r="D56" s="37" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
@@ -14719,7 +14727,7 @@
       <c r="F56" s="8" t="n"/>
     </row>
     <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>安全施設</t>
         </is>
@@ -14730,7 +14738,7 @@
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
-      <c r="D57" s="36" t="inlineStr">
+      <c r="D57" s="37" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
@@ -14743,7 +14751,7 @@
       <c r="F57" s="8" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>消火設備</t>
         </is>
@@ -14754,7 +14762,7 @@
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
-      <c r="D58" s="36" t="inlineStr">
+      <c r="D58" s="37" t="inlineStr">
         <is>
           <t>発電機各台に1本以上</t>
         </is>
@@ -14767,7 +14775,7 @@
       <c r="F58" s="8" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>油流出対策</t>
         </is>
@@ -14778,7 +14786,7 @@
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
-      <c r="D59" s="36" t="inlineStr">
+      <c r="D59" s="37" t="inlineStr">
         <is>
           <t>一式</t>
         </is>
@@ -14791,7 +14799,7 @@
       <c r="F59" s="8" t="n"/>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>夜間照明</t>
         </is>
@@ -14802,7 +14810,7 @@
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
-      <c r="D60" s="36" t="inlineStr">
+      <c r="D60" s="37" t="inlineStr">
         <is>
           <t>一式</t>
         </is>

--- a/停電作業計画書_第2回_補給倉庫棟.xlsx
+++ b/停電作業計画書_第2回_補給倉庫棟.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'7.タイムスケジュール'!$A$1:$I$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'8.配置図'!$A$1:$F$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'9.品質管理'!$A$1:$G$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'10.チェックリスト'!$A$1:$F$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'10.チェックリスト'!$A$1:$F$84</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'11.測定記録'!$A$1:$G$97</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'12.作業員名簿'!$A$1:$H$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'※要確認事項'!$A$1:$D$20</definedName>
@@ -343,7 +343,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2565,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3622,7 +3622,7 @@
       <c r="E68" s="25" t="inlineStr"/>
       <c r="F68" s="25" t="inlineStr"/>
     </row>
-    <row r="69" ht="29.84" customHeight="1">
+    <row r="69" ht="42.76" customHeight="1">
       <c r="A69" s="25" t="inlineStr">
         <is>
           <t>7</t>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>作業用接地（短絡接地器具）をすべて取り外し、数量を照合したか</t>
+          <t>発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続を、高圧停電・作業用接地中に完了したか</t>
         </is>
       </c>
       <c r="C69" s="25" t="inlineStr"/>
@@ -3638,7 +3638,7 @@
       <c r="E69" s="25" t="inlineStr"/>
       <c r="F69" s="25" t="inlineStr"/>
     </row>
-    <row r="70" ht="21" customHeight="1">
+    <row r="70" ht="29.84" customHeight="1">
       <c r="A70" s="25" t="inlineStr">
         <is>
           <t>8</t>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B70" s="26" t="inlineStr">
         <is>
-          <t>絶縁抵抗測定を行い、規定値以上であることを確認したか</t>
+          <t>作業用接地（短絡接地器具）をすべて取り外し、数量を照合したか</t>
         </is>
       </c>
       <c r="C70" s="25" t="inlineStr"/>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>作業員全員を安全な位置へ退避させ、復電を周知したか</t>
+          <t>絶縁抵抗測定を行い、規定値以上であることを確認したか</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr"/>
@@ -3670,7 +3670,7 @@
       <c r="E71" s="25" t="inlineStr"/>
       <c r="F71" s="25" t="inlineStr"/>
     </row>
-    <row r="72" ht="29.84" customHeight="1">
+    <row r="72" ht="21" customHeight="1">
       <c r="A72" s="25" t="inlineStr">
         <is>
           <t>10</t>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>部隊・監督官及び中央監視盤の監視者へ復電の連絡を行ったか</t>
+          <t>作業員全員を安全な位置へ退避させ、復電を周知したか</t>
         </is>
       </c>
       <c r="C72" s="25" t="inlineStr"/>
@@ -3686,66 +3686,66 @@
       <c r="E72" s="25" t="inlineStr"/>
       <c r="F72" s="25" t="inlineStr"/>
     </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="32" t="inlineStr">
+    <row r="73" ht="29.84" customHeight="1">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>部隊・監督官及び中央監視盤の監視者へ復電の連絡を行ったか</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr"/>
+      <c r="D73" s="25" t="inlineStr"/>
+      <c r="E73" s="25" t="inlineStr"/>
+      <c r="F73" s="25" t="inlineStr"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>10.6　復電後・終業時</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B75" s="24" t="inlineStr">
+      <c r="B76" s="24" t="inlineStr">
         <is>
           <t>確　認　項　目</t>
         </is>
       </c>
-      <c r="C75" s="24" t="inlineStr">
+      <c r="C76" s="24" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="D75" s="24" t="inlineStr">
+      <c r="D76" s="24" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="E75" s="24" t="inlineStr">
+      <c r="E76" s="24" t="inlineStr">
         <is>
           <t>作業指揮者</t>
         </is>
       </c>
-      <c r="F75" s="24" t="inlineStr">
+      <c r="F76" s="24" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="42.76" customHeight="1">
-      <c r="A76" s="25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B76" s="26" t="inlineStr">
-        <is>
-          <t>発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続を、高圧停電・作業用接地中に完了したか</t>
-        </is>
-      </c>
-      <c r="C76" s="25" t="inlineStr"/>
-      <c r="D76" s="25" t="inlineStr"/>
-      <c r="E76" s="25" t="inlineStr"/>
-      <c r="F76" s="25" t="inlineStr"/>
     </row>
     <row r="77" ht="29.84" customHeight="1">
       <c r="A77" s="25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B77" s="26" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="78" ht="29.84" customHeight="1">
       <c r="A78" s="25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B78" s="26" t="inlineStr">
@@ -3777,12 +3777,12 @@
     <row r="79" ht="29.84" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>負荷を順次投入し、補給倉庫棟の機能の正常を部隊立会のもと確認したか</t>
+          <t>④の2号機接続に用いた分岐MCCBは、仮設ケーブルの撤去を確認してから施錠解除・投入したか</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr"/>
@@ -3790,15 +3790,15 @@
       <c r="E79" s="25" t="inlineStr"/>
       <c r="F79" s="25" t="inlineStr"/>
     </row>
-    <row r="80" ht="21" customHeight="1">
+    <row r="80" ht="29.84" customHeight="1">
       <c r="A80" s="25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B80" s="26" t="inlineStr">
         <is>
-          <t>変圧器の温度計・警報接点の動作を確認したか</t>
+          <t>負荷を順次投入し、補給倉庫棟の機能の正常を部隊立会のもと確認したか</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr"/>
@@ -3809,12 +3809,12 @@
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>操作禁止札・施錠具を撤去したか</t>
+          <t>変圧器の温度計・警報接点の動作を確認したか</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr"/>
@@ -3825,12 +3825,12 @@
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B82" s="26" t="inlineStr">
         <is>
-          <t>測定記録・写真を整理し、監督官の確認を受けたか</t>
+          <t>操作禁止札・施錠具を撤去したか</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr"/>
@@ -3841,26 +3841,42 @@
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>現場を清掃し、安全施設を適正な状態に戻したか</t>
+          <t>測定記録・写真を整理し、監督官の確認を受けたか</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr"/>
       <c r="D83" s="25" t="inlineStr"/>
       <c r="E83" s="25" t="inlineStr"/>
       <c r="F83" s="25" t="inlineStr"/>
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>現場を清掃し、安全施設を適正な状態に戻したか</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="inlineStr"/>
+      <c r="D84" s="25" t="inlineStr"/>
+      <c r="E84" s="25" t="inlineStr"/>
+      <c r="F84" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
@@ -3908,10 +3924,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18.6" customHeight="1">
+    <row r="2" ht="32.2" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>工事名:舞鶴外（6）照明改修等電気その他工事　　作業場所:舞鶴航空基地　補給倉庫棟　電気室</t>
+          <t>工事名:舞鶴外（6）照明改修等電気その他工事
+作業場所:海上自衛隊　舞鶴航空基地　補給倉庫棟　電気室（京都府舞鶴市）</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4153,7 @@
       <c r="F17" s="25" t="inlineStr"/>
       <c r="G17" s="25" t="inlineStr"/>
     </row>
-    <row r="18" ht="29.84" customHeight="1">
+    <row r="18" ht="55.68" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
           <t>2次導体（FBU）母線側接続部（②③④）</t>
@@ -4153,7 +4170,7 @@
       <c r="F18" s="25" t="inlineStr"/>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>商用切替時</t>
+          <t>12/6発電機切離し後（高圧停電・接地中）</t>
         </is>
       </c>
     </row>
@@ -6718,34 +6735,34 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>項　　目</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>内　容　（未確定・調査中の内容）</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>反映先シート</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.68" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+    <row r="5" ht="52.96" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>止められない負荷</t>
         </is>
@@ -6755,63 +6772,63 @@
           <t>CVCF室・電算機室等の停止できない負荷は現在調査中。結果により仮設切替時（12/5　9:00～10:30頃）・商用復旧時（12/6　15:45～16:45頃）の停電への対応（事前停止・UPS保持等）を定め、部隊の承諾を得る。</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr">
         <is>
           <t>2.2・6.3・7</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55.68" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+    <row r="6" ht="65.2" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>低圧電灯盤④への2台接続</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>2台が並列とならないよう、1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続する計画とした。2号機で受け持つ分岐回路（負荷）と、その回路の負荷容量を確認する。</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr">
+          <t>2台が並列とならないよう、1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続する計画とした。2号機で受け持つ分岐回路（負荷）と、その回路の負荷容量、及びCET150sqが当該MCCB負荷側端子に接続できるか（端子サイズ・圧着端子）を確認する。</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>2.3・5.4・6.3・7・8</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.68" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+    <row r="7" ht="65.2" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>仮設ケーブルの接続点</t>
         </is>
       </c>
       <c r="C7" s="39" t="inlineStr">
         <is>
-          <t>ED-02注記2）は「低圧側に仮設発電機を接続」とのみ記載。本書では②③を低圧母線（FBU負荷側）、④を52-L二次側（★4A　CT（L）取替え範囲を無電圧とするため）とした。別川製作所・電気主任技術者と接続位置を確認する。</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
+          <t>ED-02注記2）は「低圧側に仮設発電機を接続」とのみ記載。本書では②③を低圧母線（FBU負荷側）、④は1号機を52-L二次側（★4A　CT（L）取替え範囲を無電圧とするため）、2号機を特定分岐MCCB負荷側（MCCB開放・施錠）とした。別川製作所・電気主任技術者と接続位置を確認する。</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>2.3・5・6・7・8</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42.76" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+    <row r="8" ht="40.72" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>絶縁距離不足の記載</t>
         </is>
@@ -6821,19 +6838,19 @@
           <t>別川製作所　内部機器配置図（3）（P-15　No.2低圧動力盤）に「▲絶縁距離不足！」の記載あり。対策内容を別川製作所に確認する。</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>6・9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="29.84" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+    <row r="9" ht="28.48" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>関西電気保安協会</t>
         </is>
@@ -6843,19 +6860,19 @@
           <t>担当者名・連絡先が未記入。人数は2名で仮置き。試験項目・試験電圧（絶縁耐力）・継電器整定値を事前に協議する。</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>3・4・7・11・12</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.68" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+    <row r="10" ht="52.96" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>夜間監視員・給油</t>
         </is>
@@ -6865,19 +6882,19 @@
           <t>夜間監視員の氏名・人数・交代体制（日中作業者とは別）、及び発電機の燃料タンク容量と給油方法・給油時期を確定する。軽油は発電機タンク内を含め200L以上で少量危険物の届出、1,000L以上で消防署の仮貯蔵・仮取扱い承認が必要。</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>2.3・3・7・8・12</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42.76" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+    <row r="11" ht="40.72" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>燃料数量</t>
         </is>
@@ -6887,19 +6904,19 @@
           <t>打合せにより2日間で算定（24h×2日×2台×70.4L/h=6,758.4L）。ED-02注記「停電作業7日間（式は3日）」との相違について監督官の了承を得る。</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>2.3・8</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="29.84" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+    <row r="12" ht="28.48" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>既設変圧器の質量</t>
         </is>
@@ -6909,19 +6926,19 @@
           <t>不明のため「銘板確認による」と記載。銘板確認後に揚重計画へ反映する。</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="55.68" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+    <row r="13" ht="52.96" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>揚重機械の能力・運搬</t>
         </is>
@@ -6931,19 +6948,19 @@
           <t>2tユニック車の定格荷重と作業半径（T-1　1,140kg）、設置位置・アウトリガー張出し、チェーンブロックの吊元を現地で確認する。新設変圧器の運搬（メーカー納入便か2tユニック車での複数回運搬か）を確定する。</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>5.4・6.5</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>関西テクノの従事日</t>
         </is>
@@ -6953,19 +6970,19 @@
           <t>局舎Aと同様に停電作業日（12/5・6）の1名で仮置き。</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>3・7・12</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="29.84" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+    <row r="15" ht="28.48" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>作業員の氏名・資格</t>
         </is>
@@ -6975,19 +6992,19 @@
           <t>別川製作所6名・ARワーク5名・㈱アートの氏名・年齢・保有資格は確定後に記入する。</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="29.84" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="16" ht="28.48" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>休日作業の手続き</t>
         </is>
@@ -6997,19 +7014,19 @@
           <t>作業日が土・日曜日のため、基地への入門・立入申請、休日の部隊連絡先（当直等）を確認する。</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>2.2・4</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="42.76" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+    <row r="17" ht="40.72" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>中央監視・制御電源</t>
         </is>
@@ -7019,19 +7036,19 @@
           <t>停電中の中央監視盤への警報発報の連絡先、及び高圧受電盤の制御電源（UPS　AC100V）の供給元・停電中の扱いを確認する。</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
@@ -7041,19 +7058,19 @@
           <t>12月8日（火）で記載。部隊との調整により決定する。</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="68.59999999999999" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+    <row r="19" ht="52.96" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>12/6の終了時刻</t>
         </is>
@@ -7063,19 +7080,19 @@
           <t>保安協会の試験・検査（15:00頃～）終了後に復電・商用切替を行うため、12/6の作業終了は17:00頃の予定。部隊・監督官の了承を得る。試験が長引く場合の判断時刻（例:16:30）と予備日（12/8）への持越し基準を事前に協議する。</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>表紙・2・7</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="29.84" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+    <row r="20" ht="28.48" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>残り3回の停電作業</t>
         </is>
@@ -7085,7 +7102,7 @@
           <t>本書は第2回（補給倉庫棟）。第3回以降の対象施設・日程が決まり次第、同様式で作成する。</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -8533,7 +8550,7 @@
     <row r="68" ht="86.59999999999999" customHeight="1">
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>①　仮設発電機400kVA×2台（三相出力・単相出力付）を補給倉庫棟外部に設置し、CET150sq（FEP100）×6条にて各盤の低圧側へ接続する（1号機→②2条・④1条/2号機→③2条・④1条）。接続点は②③が低圧母線（FBU負荷側）、④は1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCBは開放・施錠）として2台が並列とならないようにし、変圧器2次導体（FBU）の取外しにより変圧器への逆送を防止する。低圧電灯盤④（1φ3W　210-105V）へは発電機の単相出力より送電する。</t>
+          <t>①　補給倉庫棟外部に仮設発電機400kVA×2台（三相出力・単相出力付）を設置する。仮設ケーブルはCET150sq（FEP100）×6条とし、各盤の低圧側へ接続する（1号機→②2条・④1条/2号機→③2条・④1条）。接続点は②③が低圧母線（FBU負荷側）、④は1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCBは開放・施錠）として2台が並列とならないようにし、変圧器2次導体（FBU）の取外しにより変圧器への逆送を防止する。低圧電灯盤④（1φ3W　210-105V）へは発電機の単相出力より送電する。</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10420,7 @@
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>最大1,140kg（T-1）の変圧器は指定のつり耳を使用して吊り、吊り角度60度以内とする。吊り荷の下へ立ち入らせず、作業半径を区画する。玉掛け・クレーン運転は有資格者が行い、合図者を専任する。</t>
+          <t>最大1,140kg（T-1）の変圧器は指定のつり耳を使用して吊り、吊り角度60度以内とする。吊り荷の下へ立ち入らせず、作業半径を区画する。玉掛け・クレーン運転は有資格者が行い、合図者を専任する</t>
         </is>
       </c>
       <c r="D34" s="31" t="inlineStr">
@@ -13853,7 +13870,7 @@
       </c>
       <c r="I69" s="31" t="inlineStr"/>
     </row>
-    <row r="70" ht="28.48" customHeight="1">
+    <row r="70" ht="40.72" customHeight="1">
       <c r="A70" s="31" t="inlineStr">
         <is>
           <t>19</t>
@@ -13882,7 +13899,7 @@
       <c r="F70" s="31" t="inlineStr"/>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>MCCBを順次投入、部隊立会のもと機能確認。監督官・部隊へ完了報告</t>
+          <t>MCCBを順次投入（④の2号機接続用分岐MCCBは仮設ケーブル撤去確認後に施錠解除・投入）、部隊立会のもと機能確認・完了報告</t>
         </is>
       </c>
       <c r="H70" s="31" t="inlineStr">

--- a/停電作業計画書_第2回_補給倉庫棟.xlsx
+++ b/停電作業計画書_第2回_補給倉庫棟.xlsx
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>④の2号機接続に用いた分岐MCCBは、仮設ケーブルの撤去を確認してから施錠解除・投入したか</t>
+          <t>④の2号機接続に用いた分岐MCCBは、仮設ケーブルの盤側切離しを確認してから施錠解除・投入したか</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       <c r="F18" s="25" t="inlineStr"/>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>12/6発電機切離し後（高圧停電・接地中）</t>
+          <t>12/6発電機切離し後（高圧停電中）</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       <c r="F70" s="31" t="inlineStr"/>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>MCCBを順次投入（④の2号機接続用分岐MCCBは仮設ケーブル撤去確認後に施錠解除・投入）、部隊立会のもと機能確認・完了報告</t>
+          <t>MCCBを順次投入（④の2号機接続用分岐MCCBは仮設ケーブル盤側切離し確認後に施錠解除・投入）、部隊立会のもと機能確認・完了報告</t>
         </is>
       </c>
       <c r="H70" s="31" t="inlineStr">

--- a/停電作業計画書_第2回_補給倉庫棟.xlsx
+++ b/停電作業計画書_第2回_補給倉庫棟.xlsx
@@ -6791,7 +6791,7 @@
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>2台が並列とならないよう、1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続する計画とした。2号機で受け持つ分岐回路（負荷）と、その回路の負荷容量、及びCET150sqが当該MCCB負荷側端子に接続できるか（端子サイズ・圧着端子）を確認する。</t>
+          <t>1号機を52-L二次側（分岐母線）、2号機を④の特定分岐回路のMCCB負荷側（当該MCCB開放・施錠）に接続する方針で了承済み。2号機で受け持つ分岐回路（負荷）とその負荷容量、及びCET150sqが当該MCCB負荷側端子に接続できるか（端子サイズ・圧着端子）を確認する。</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
@@ -7064,7 +7064,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52.96" customHeight="1">
+    <row r="19" ht="40.72" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>15</t>
@@ -7072,17 +7072,17 @@
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>12/6の終了時刻</t>
+          <t>試験延長時の判断</t>
         </is>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>保安協会の試験・検査（15:00頃～）終了後に復電・商用切替を行うため、12/6の作業終了は17:00頃の予定。部隊・監督官の了承を得る。試験が長引く場合の判断時刻（例:16:30）と予備日（12/8）への持越し基準を事前に協議する。</t>
+          <t>12/6は17:00頃終了で了承済み。保安協会の試験・検査が長引く場合の判断時刻（例:16:30）と予備日（12/8）への持越し基準を事前に協議する。</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>表紙・2・7</t>
+          <t>2・7</t>
         </is>
       </c>
     </row>
